--- a/ITX.MC.xlsx
+++ b/ITX.MC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D09F8C8-2E46-4B12-8374-64084317917A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58E19782-CF03-4F9B-9358-218FED79A078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{D8A593F9-CE2E-4D8C-B815-D7E0264BAFFB}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{D8A593F9-CE2E-4D8C-B815-D7E0264BAFFB}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -113,7 +113,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="204">
   <si>
     <t>Inditex</t>
   </si>
@@ -722,13 +722,16 @@
   </si>
   <si>
     <t>New Brand: Lefties - high budget Zara pieces</t>
+  </si>
+  <si>
+    <t>FY25</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="10">
+  <numFmts count="11">
     <numFmt numFmtId="164" formatCode="#,##0.0;[Red]#,##0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.00_);\(#,##0.00\)"/>
     <numFmt numFmtId="166" formatCode="##\F\Y"/>
@@ -739,14 +742,21 @@
     <numFmt numFmtId="171" formatCode="#,##0.0;\(#,##0.0\)"/>
     <numFmt numFmtId="172" formatCode="#,##0;[Red]#,##0"/>
     <numFmt numFmtId="173" formatCode="#,##0;\(#,##0\)"/>
+    <numFmt numFmtId="174" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1085,132 +1095,134 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="173" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="171" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="173" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="173" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="4" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="3" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="170" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="170" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="3" fillId="3" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="15" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="8" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="16" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="9" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="9" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -1234,16 +1246,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>28576</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
+      <xdr:rowOff>144463</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>15875</xdr:colOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>34926</xdr:colOff>
       <xdr:row>120</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>157163</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1258,8 +1270,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12420600" y="63500"/>
-          <a:ext cx="6350" cy="22682200"/>
+          <a:off x="14906626" y="144463"/>
+          <a:ext cx="6350" cy="19443700"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -1284,16 +1296,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>4763</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>33338</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>11113</xdr:colOff>
-      <xdr:row>121</xdr:row>
-      <xdr:rowOff>98425</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>39688</xdr:colOff>
+      <xdr:row>122</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1308,7 +1320,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8986838" y="247650"/>
+          <a:off x="9625013" y="400050"/>
           <a:ext cx="6350" cy="19443700"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1696,8 +1708,8 @@
       <c r="I3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="J3" s="79">
-        <v>54.86</v>
+      <c r="J3" s="75">
+        <v>52.82</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -1713,11 +1725,11 @@
       <c r="I4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="J4" s="5">
-        <v>3115.9987160000001</v>
-      </c>
-      <c r="K4" s="80" t="s">
-        <v>193</v>
+      <c r="J4" s="81">
+        <v>3116.0914859999998</v>
+      </c>
+      <c r="K4" s="82" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -1735,7 +1747,7 @@
       </c>
       <c r="J5" s="5">
         <f>J4*J3</f>
-        <v>170943.68955976001</v>
+        <v>164591.95229051998</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -1743,11 +1755,11 @@
         <v>4</v>
       </c>
       <c r="J6" s="5">
-        <f>5951+5318</f>
-        <v>11269</v>
-      </c>
-      <c r="K6" s="80" t="s">
-        <v>193</v>
+        <f>5276+5684</f>
+        <v>10960</v>
+      </c>
+      <c r="K6" s="82" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -1771,11 +1783,10 @@
         <v>5</v>
       </c>
       <c r="J7" s="5">
-        <f>1+0</f>
-        <v>1</v>
-      </c>
-      <c r="K7" s="80" t="s">
-        <v>193</v>
+        <v>2</v>
+      </c>
+      <c r="K7" s="82" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -1795,7 +1806,7 @@
       </c>
       <c r="J8" s="5">
         <f>J5-J6+J7</f>
-        <v>159675.68955976001</v>
+        <v>153633.95229051998</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -1872,7 +1883,7 @@
       <c r="G13" s="19"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B15" s="81" t="s">
+      <c r="B15" s="76" t="s">
         <v>202</v>
       </c>
     </row>
@@ -1897,7 +1908,7 @@
     <col min="22" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>90</v>
       </c>
@@ -1922,7 +1933,7 @@
       <c r="T1" s="2"/>
       <c r="U1" s="2"/>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B2" s="2"/>
       <c r="C2" s="6" t="s">
         <v>8</v>
@@ -2010,7 +2021,7 @@
       </c>
       <c r="AB2" s="20"/>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B3" s="74" t="s">
         <v>195</v>
       </c>
@@ -2040,17 +2051,26 @@
       <c r="Q3" s="20"/>
       <c r="R3" s="20"/>
       <c r="S3" s="20"/>
-      <c r="T3" s="20"/>
-      <c r="U3" s="20"/>
-      <c r="V3" s="20"/>
-      <c r="W3" s="20"/>
-      <c r="X3" s="20"/>
-      <c r="Y3" s="20"/>
-      <c r="Z3" s="20"/>
-      <c r="AA3" s="20"/>
-      <c r="AB3" s="20"/>
-    </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="T3" s="21"/>
+      <c r="U3" s="21"/>
+      <c r="V3" s="21">
+        <f>1550+391+209</f>
+        <v>2150</v>
+      </c>
+      <c r="W3" s="21">
+        <f>1500+374+215</f>
+        <v>2089</v>
+      </c>
+      <c r="X3" s="21"/>
+      <c r="Y3" s="21"/>
+      <c r="Z3" s="21"/>
+      <c r="AA3" s="21"/>
+      <c r="AB3" s="21"/>
+      <c r="AC3" s="21"/>
+      <c r="AD3" s="21"/>
+      <c r="AE3" s="21"/>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B4" s="74" t="s">
         <v>196</v>
       </c>
@@ -2077,17 +2097,24 @@
       <c r="Q4" s="20"/>
       <c r="R4" s="20"/>
       <c r="S4" s="20"/>
-      <c r="T4" s="20"/>
-      <c r="U4" s="20"/>
-      <c r="V4" s="20"/>
-      <c r="W4" s="20"/>
-      <c r="X4" s="20"/>
-      <c r="Y4" s="20"/>
-      <c r="Z4" s="20"/>
-      <c r="AA4" s="20"/>
-      <c r="AB4" s="20"/>
-    </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="T4" s="21"/>
+      <c r="U4" s="21"/>
+      <c r="V4" s="21">
+        <v>800</v>
+      </c>
+      <c r="W4" s="21">
+        <v>791</v>
+      </c>
+      <c r="X4" s="21"/>
+      <c r="Y4" s="21"/>
+      <c r="Z4" s="21"/>
+      <c r="AA4" s="21"/>
+      <c r="AB4" s="21"/>
+      <c r="AC4" s="21"/>
+      <c r="AD4" s="21"/>
+      <c r="AE4" s="21"/>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B5" s="74" t="s">
         <v>197</v>
       </c>
@@ -2114,17 +2141,24 @@
       <c r="Q5" s="20"/>
       <c r="R5" s="20"/>
       <c r="S5" s="20"/>
-      <c r="T5" s="20"/>
-      <c r="U5" s="20"/>
-      <c r="V5" s="20"/>
-      <c r="W5" s="20"/>
-      <c r="X5" s="20"/>
-      <c r="Y5" s="20"/>
-      <c r="Z5" s="20"/>
-      <c r="AA5" s="20"/>
-      <c r="AB5" s="20"/>
-    </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="T5" s="21"/>
+      <c r="U5" s="21"/>
+      <c r="V5" s="21">
+        <v>528</v>
+      </c>
+      <c r="W5" s="21">
+        <v>511</v>
+      </c>
+      <c r="X5" s="21"/>
+      <c r="Y5" s="21"/>
+      <c r="Z5" s="21"/>
+      <c r="AA5" s="21"/>
+      <c r="AB5" s="21"/>
+      <c r="AC5" s="21"/>
+      <c r="AD5" s="21"/>
+      <c r="AE5" s="21"/>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="74" t="s">
         <v>198</v>
       </c>
@@ -2151,17 +2185,24 @@
       <c r="Q6" s="20"/>
       <c r="R6" s="20"/>
       <c r="S6" s="20"/>
-      <c r="T6" s="20"/>
-      <c r="U6" s="20"/>
-      <c r="V6" s="20"/>
-      <c r="W6" s="20"/>
-      <c r="X6" s="20"/>
-      <c r="Y6" s="20"/>
-      <c r="Z6" s="20"/>
-      <c r="AA6" s="20"/>
-      <c r="AB6" s="20"/>
-    </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="T6" s="21"/>
+      <c r="U6" s="21"/>
+      <c r="V6" s="21">
+        <v>854</v>
+      </c>
+      <c r="W6" s="21">
+        <v>852</v>
+      </c>
+      <c r="X6" s="21"/>
+      <c r="Y6" s="21"/>
+      <c r="Z6" s="21"/>
+      <c r="AA6" s="21"/>
+      <c r="AB6" s="21"/>
+      <c r="AC6" s="21"/>
+      <c r="AD6" s="21"/>
+      <c r="AE6" s="21"/>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B7" s="74" t="s">
         <v>199</v>
       </c>
@@ -2188,17 +2229,24 @@
       <c r="Q7" s="20"/>
       <c r="R7" s="20"/>
       <c r="S7" s="20"/>
-      <c r="T7" s="20"/>
-      <c r="U7" s="20"/>
-      <c r="V7" s="20"/>
-      <c r="W7" s="20"/>
-      <c r="X7" s="20"/>
-      <c r="Y7" s="20"/>
-      <c r="Z7" s="20"/>
-      <c r="AA7" s="20"/>
-      <c r="AB7" s="20"/>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="T7" s="21"/>
+      <c r="U7" s="21"/>
+      <c r="V7" s="21">
+        <v>835</v>
+      </c>
+      <c r="W7" s="21">
+        <v>834</v>
+      </c>
+      <c r="X7" s="21"/>
+      <c r="Y7" s="21"/>
+      <c r="Z7" s="21"/>
+      <c r="AA7" s="21"/>
+      <c r="AB7" s="21"/>
+      <c r="AC7" s="21"/>
+      <c r="AD7" s="21"/>
+      <c r="AE7" s="21"/>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B8" s="74" t="s">
         <v>200</v>
       </c>
@@ -2225,17 +2273,24 @@
       <c r="Q8" s="20"/>
       <c r="R8" s="20"/>
       <c r="S8" s="20"/>
-      <c r="T8" s="20"/>
-      <c r="U8" s="20"/>
-      <c r="V8" s="20"/>
-      <c r="W8" s="20"/>
-      <c r="X8" s="20"/>
-      <c r="Y8" s="20"/>
-      <c r="Z8" s="20"/>
-      <c r="AA8" s="20"/>
-      <c r="AB8" s="20"/>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="T8" s="21"/>
+      <c r="U8" s="21"/>
+      <c r="V8" s="21">
+        <v>396</v>
+      </c>
+      <c r="W8" s="21">
+        <v>383</v>
+      </c>
+      <c r="X8" s="21"/>
+      <c r="Y8" s="21"/>
+      <c r="Z8" s="21"/>
+      <c r="AA8" s="21"/>
+      <c r="AB8" s="21"/>
+      <c r="AC8" s="21"/>
+      <c r="AD8" s="21"/>
+      <c r="AE8" s="21"/>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B9" s="74" t="s">
         <v>201</v>
       </c>
@@ -2262,17 +2317,24 @@
       <c r="Q9" s="20"/>
       <c r="R9" s="20"/>
       <c r="S9" s="20"/>
-      <c r="T9" s="20"/>
-      <c r="U9" s="20"/>
-      <c r="V9" s="20"/>
-      <c r="W9" s="20"/>
-      <c r="X9" s="20"/>
-      <c r="Y9" s="20"/>
-      <c r="Z9" s="20"/>
-      <c r="AA9" s="20"/>
-      <c r="AB9" s="20"/>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="T9" s="21"/>
+      <c r="U9" s="21"/>
+      <c r="V9" s="21">
+        <v>0</v>
+      </c>
+      <c r="W9" s="21">
+        <v>0</v>
+      </c>
+      <c r="X9" s="21"/>
+      <c r="Y9" s="21"/>
+      <c r="Z9" s="21"/>
+      <c r="AA9" s="21"/>
+      <c r="AB9" s="21"/>
+      <c r="AC9" s="21"/>
+      <c r="AD9" s="21"/>
+      <c r="AE9" s="21"/>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B10" s="27" t="s">
         <v>135</v>
       </c>
@@ -2331,29 +2393,28 @@
         <v>5563</v>
       </c>
       <c r="W10" s="28">
-        <f>V10*0.97</f>
-        <v>5396.11</v>
+        <v>5460</v>
       </c>
       <c r="X10" s="28">
         <f t="shared" ref="X10:AA10" si="1">W10*0.97</f>
-        <v>5234.2266999999993</v>
+        <v>5296.2</v>
       </c>
       <c r="Y10" s="28">
         <f t="shared" si="1"/>
-        <v>5077.1998989999993</v>
+        <v>5137.3139999999994</v>
       </c>
       <c r="Z10" s="28">
         <f t="shared" si="1"/>
-        <v>4924.8839020299993</v>
+        <v>4983.1945799999994</v>
       </c>
       <c r="AA10" s="28">
         <f t="shared" si="1"/>
-        <v>4777.137384969099</v>
+        <v>4833.6987425999996</v>
       </c>
       <c r="AB10" s="21"/>
       <c r="AC10" s="21"/>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B11" s="3" t="s">
         <v>142</v>
       </c>
@@ -2389,9 +2450,11 @@
         <v>4557.17</v>
       </c>
       <c r="V11" s="21">
-        <v>5650.5749999999998</v>
-      </c>
-      <c r="W11" s="21"/>
+        <v>4650.5749999999998</v>
+      </c>
+      <c r="W11" s="21">
+        <v>4650.5749999999998</v>
+      </c>
       <c r="X11" s="21"/>
       <c r="Y11" s="21"/>
       <c r="Z11" s="21"/>
@@ -2399,7 +2462,7 @@
       <c r="AB11" s="21"/>
       <c r="AC11" s="21"/>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B12" s="3" t="s">
         <v>137</v>
       </c>
@@ -2445,29 +2508,29 @@
         <v>28432</v>
       </c>
       <c r="W12" s="21">
-        <f t="shared" ref="W12:AA12" si="3">W13*W10</f>
-        <v>28957.991999999998</v>
+        <f t="shared" ref="W12" si="3">W29-W15</f>
+        <v>29149.919999999998</v>
       </c>
       <c r="X12" s="21">
-        <f t="shared" si="3"/>
-        <v>29493.714852000001</v>
+        <f t="shared" ref="W12:AA12" si="4">X13*X10</f>
+        <v>29689.193519999997</v>
       </c>
       <c r="Y12" s="21">
-        <f t="shared" si="3"/>
-        <v>30039.348576762</v>
+        <f t="shared" si="4"/>
+        <v>30238.443600119994</v>
       </c>
       <c r="Z12" s="21">
-        <f t="shared" si="3"/>
-        <v>30595.076525432101</v>
+        <f t="shared" si="4"/>
+        <v>30797.854806722215</v>
       </c>
       <c r="AA12" s="21">
-        <f t="shared" si="3"/>
-        <v>31161.085441152594</v>
+        <f t="shared" si="4"/>
+        <v>31367.61512064658</v>
       </c>
       <c r="AB12" s="21"/>
       <c r="AC12" s="21"/>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>138</v>
       </c>
@@ -2485,23 +2548,23 @@
       <c r="N13" s="21"/>
       <c r="O13" s="21"/>
       <c r="P13" s="21">
-        <f t="shared" ref="P13:T13" si="4">P12/P10</f>
+        <f t="shared" ref="P13:T13" si="5">P12/P10</f>
         <v>3.0634178905206944</v>
       </c>
       <c r="Q13" s="21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.2650957290132547</v>
       </c>
       <c r="R13" s="21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.0210865426856057</v>
       </c>
       <c r="S13" s="21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.1211980855334258</v>
       </c>
       <c r="T13" s="21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4.2595012897678419</v>
       </c>
       <c r="U13" s="21">
@@ -2513,29 +2576,29 @@
         <v>5.1109113787524718</v>
       </c>
       <c r="W13" s="21">
-        <f t="shared" ref="W13:AA13" si="5">V13*1.05</f>
-        <v>5.3664569476900956</v>
+        <f>W12/W10</f>
+        <v>5.3388131868131863</v>
       </c>
       <c r="X13" s="21">
-        <f t="shared" si="5"/>
-        <v>5.6347797950746008</v>
+        <f t="shared" ref="W13:AA13" si="6">W13*1.05</f>
+        <v>5.6057538461538456</v>
       </c>
       <c r="Y13" s="21">
-        <f t="shared" si="5"/>
-        <v>5.9165187848283312</v>
+        <f t="shared" si="6"/>
+        <v>5.8860415384615381</v>
       </c>
       <c r="Z13" s="21">
-        <f t="shared" si="5"/>
-        <v>6.212344724069748</v>
+        <f t="shared" si="6"/>
+        <v>6.180343615384615</v>
       </c>
       <c r="AA13" s="21">
-        <f t="shared" si="5"/>
-        <v>6.5229619602732356</v>
+        <f t="shared" si="6"/>
+        <v>6.4893607961538464</v>
       </c>
       <c r="AB13" s="21"/>
       <c r="AC13" s="21"/>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B14" s="3" t="s">
         <v>141</v>
       </c>
@@ -2553,23 +2616,23 @@
       <c r="N14" s="21"/>
       <c r="O14" s="21"/>
       <c r="P14" s="21">
-        <f t="shared" ref="P14:T14" si="6">P12/P11</f>
+        <f t="shared" ref="P14:T14" si="7">P12/P11</f>
         <v>4.6240680069511155</v>
       </c>
       <c r="Q14" s="21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4.7942372430865241</v>
       </c>
       <c r="R14" s="21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2.8595959520618845</v>
       </c>
       <c r="S14" s="21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4.2630389504185544</v>
       </c>
       <c r="T14" s="21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>5.5370037452848617</v>
       </c>
       <c r="U14" s="21">
@@ -2578,9 +2641,12 @@
       </c>
       <c r="V14" s="21">
         <f>V12/V11</f>
-        <v>5.0317003136848903</v>
-      </c>
-      <c r="W14" s="21"/>
+        <v>6.1136526128489495</v>
+      </c>
+      <c r="W14" s="21">
+        <f>W12/W11</f>
+        <v>6.2680249216494737</v>
+      </c>
       <c r="X14" s="21"/>
       <c r="Y14" s="21"/>
       <c r="Z14" s="21"/>
@@ -2588,7 +2654,7 @@
       <c r="AB14" s="21"/>
       <c r="AC14" s="21"/>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
         <v>131</v>
       </c>
@@ -2627,29 +2693,29 @@
         <v>10200</v>
       </c>
       <c r="W15" s="21">
-        <f t="shared" ref="W15:AA15" si="7">W17*W20</f>
+        <f>W17*W20</f>
         <v>10714.08</v>
       </c>
       <c r="X15" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="W15:AA15" si="8">X17*X20</f>
         <v>11254.069632000001</v>
       </c>
       <c r="Y15" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>11821.2747414528</v>
       </c>
       <c r="Z15" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>12417.066988422022</v>
       </c>
       <c r="AA15" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>13042.887164638492</v>
       </c>
       <c r="AB15" s="21"/>
       <c r="AC15" s="21"/>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
         <v>134</v>
       </c>
@@ -2735,23 +2801,23 @@
         <v>8100</v>
       </c>
       <c r="W17" s="21">
-        <f t="shared" ref="W17:AA17" si="8">V17*1.01</f>
+        <f t="shared" ref="W17:AA17" si="9">V17*1.01</f>
         <v>8181</v>
       </c>
       <c r="X17" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>8262.81</v>
       </c>
       <c r="Y17" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>8345.4380999999994</v>
       </c>
       <c r="Z17" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>8428.892480999999</v>
       </c>
       <c r="AA17" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>8513.181405809999</v>
       </c>
       <c r="AB17" s="21"/>
@@ -2827,15 +2893,15 @@
         <v>136</v>
       </c>
       <c r="R19" s="25">
-        <f t="shared" ref="R19:T19" si="9">R15/R16</f>
+        <f t="shared" ref="R19:T19" si="10">R15/R16</f>
         <v>50</v>
       </c>
       <c r="S19" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>51.369863013698627</v>
       </c>
       <c r="T19" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>52.348993288590606</v>
       </c>
       <c r="U19" s="25">
@@ -2878,15 +2944,15 @@
         <v>136</v>
       </c>
       <c r="R20" s="25">
-        <f t="shared" ref="R20:T20" si="10">R15/R17</f>
+        <f t="shared" ref="R20:T20" si="11">R15/R17</f>
         <v>1.2452830188679245</v>
       </c>
       <c r="S20" s="25">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.2096774193548387</v>
       </c>
       <c r="T20" s="25">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.32</v>
       </c>
       <c r="U20" s="25">
@@ -2898,19 +2964,19 @@
         <v>1.2592592592592593</v>
       </c>
       <c r="W20" s="25">
-        <f t="shared" ref="W20:Z20" si="11">V20*1.04</f>
+        <f t="shared" ref="W20:Z20" si="12">V20*1.04</f>
         <v>1.3096296296296297</v>
       </c>
       <c r="X20" s="25">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.362014814814815</v>
       </c>
       <c r="Y20" s="25">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.4164954074074076</v>
       </c>
       <c r="Z20" s="25">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.473155223703704</v>
       </c>
       <c r="AA20" s="25">
@@ -2987,7 +3053,9 @@
       <c r="V22" s="21">
         <v>27778</v>
       </c>
-      <c r="W22" s="21"/>
+      <c r="W22" s="21">
+        <v>28051</v>
+      </c>
       <c r="X22" s="21"/>
       <c r="Y22" s="21"/>
       <c r="Z22" s="21"/>
@@ -3033,7 +3101,9 @@
       <c r="V23" s="21">
         <v>2469</v>
       </c>
-      <c r="W23" s="21"/>
+      <c r="W23" s="21">
+        <v>2546</v>
+      </c>
       <c r="X23" s="21"/>
       <c r="Y23" s="21"/>
       <c r="Z23" s="21"/>
@@ -3079,7 +3149,9 @@
       <c r="V24" s="21">
         <v>1960</v>
       </c>
-      <c r="W24" s="21"/>
+      <c r="W24" s="21">
+        <v>2019</v>
+      </c>
       <c r="X24" s="21"/>
       <c r="Y24" s="21"/>
       <c r="Z24" s="21"/>
@@ -3125,7 +3197,9 @@
       <c r="V25" s="21">
         <v>2930</v>
       </c>
-      <c r="W25" s="21"/>
+      <c r="W25" s="21">
+        <v>3286</v>
+      </c>
       <c r="X25" s="21"/>
       <c r="Y25" s="21"/>
       <c r="Z25" s="21"/>
@@ -3171,7 +3245,9 @@
       <c r="V26" s="21">
         <v>2664</v>
       </c>
-      <c r="W26" s="21"/>
+      <c r="W26" s="21">
+        <v>3002</v>
+      </c>
       <c r="X26" s="21"/>
       <c r="Y26" s="21"/>
       <c r="Z26" s="21"/>
@@ -3217,7 +3293,9 @@
       <c r="V27" s="21">
         <v>831</v>
       </c>
-      <c r="W27" s="21"/>
+      <c r="W27" s="21">
+        <v>960</v>
+      </c>
       <c r="X27" s="21"/>
       <c r="Y27" s="21"/>
       <c r="Z27" s="21"/>
@@ -3263,7 +3341,9 @@
       <c r="V28" s="21">
         <v>0</v>
       </c>
-      <c r="W28" s="21"/>
+      <c r="W28" s="21">
+        <v>0</v>
+      </c>
       <c r="X28" s="21"/>
       <c r="Y28" s="21"/>
       <c r="Z28" s="21"/>
@@ -3312,26 +3392,29 @@
         <f>28171-SUM(K29:L29)</f>
         <v>9814</v>
       </c>
-      <c r="N29" s="28"/>
+      <c r="N29" s="28">
+        <f>+W29-SUM(K29:M29)</f>
+        <v>11693</v>
+      </c>
       <c r="O29" s="21"/>
       <c r="P29" s="28">
-        <f t="shared" ref="P29:T29" si="12">SUM(P22:P28)</f>
+        <f t="shared" ref="P29:T29" si="13">SUM(P22:P28)</f>
         <v>26145</v>
       </c>
       <c r="Q29" s="28">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>28287</v>
       </c>
       <c r="R29" s="28">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>20402</v>
       </c>
       <c r="S29" s="28">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>27716</v>
       </c>
       <c r="T29" s="28">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>32569</v>
       </c>
       <c r="U29" s="28">
@@ -3342,24 +3425,23 @@
         <v>38632</v>
       </c>
       <c r="W29" s="28">
-        <f>W12+W15</f>
-        <v>39672.072</v>
+        <v>39864</v>
       </c>
       <c r="X29" s="28">
         <f>X12+X15</f>
-        <v>40747.784484000003</v>
+        <v>40943.263152</v>
       </c>
       <c r="Y29" s="28">
         <f>Y12+Y15</f>
-        <v>41860.623318214799</v>
+        <v>42059.718341572792</v>
       </c>
       <c r="Z29" s="28">
         <f>Z12+Z15</f>
-        <v>43012.143513854127</v>
+        <v>43214.921795144241</v>
       </c>
       <c r="AA29" s="28">
         <f>AA12+AA15</f>
-        <v>44203.972605791088</v>
+        <v>44410.502285285074</v>
       </c>
       <c r="AB29" s="21"/>
       <c r="AC29" s="21"/>
@@ -3405,7 +3487,10 @@
         <f>11361-SUM(K30:L30)</f>
         <v>3707</v>
       </c>
-      <c r="N30" s="21"/>
+      <c r="N30" s="83">
+        <f>+W30-SUM(K30:M30)</f>
+        <v>5281</v>
+      </c>
       <c r="O30" s="21"/>
       <c r="P30" s="21">
         <v>11329</v>
@@ -3428,7 +3513,9 @@
       <c r="V30" s="21">
         <v>16288</v>
       </c>
-      <c r="W30" s="21"/>
+      <c r="W30" s="21">
+        <v>16642</v>
+      </c>
       <c r="X30" s="21"/>
       <c r="Y30" s="21"/>
       <c r="Z30" s="21"/>
@@ -3441,19 +3528,19 @@
         <v>24</v>
       </c>
       <c r="C31" s="21">
-        <f t="shared" ref="C31:J31" si="13">C29-C30</f>
+        <f t="shared" ref="C31:J31" si="14">C29-C30</f>
         <v>4603</v>
       </c>
       <c r="D31" s="21">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5197</v>
       </c>
       <c r="E31" s="21">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5402</v>
       </c>
       <c r="F31" s="21">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5558</v>
       </c>
       <c r="G31" s="21">
@@ -3465,45 +3552,48 @@
         <v>5601</v>
       </c>
       <c r="I31" s="21">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5749</v>
       </c>
       <c r="J31" s="21">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>6053</v>
       </c>
       <c r="K31" s="21">
-        <f t="shared" ref="K31:M31" si="14">K29-K30</f>
+        <f t="shared" ref="K31:N31" si="15">K29-K30</f>
         <v>5012</v>
       </c>
       <c r="L31" s="21">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>5691</v>
       </c>
       <c r="M31" s="21">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>6107</v>
       </c>
-      <c r="N31" s="21"/>
+      <c r="N31" s="21">
+        <f t="shared" si="15"/>
+        <v>6412</v>
+      </c>
       <c r="O31" s="21"/>
       <c r="P31" s="21">
-        <f t="shared" ref="P31:T31" si="15">P29-P30</f>
+        <f t="shared" ref="P31:T31" si="16">P29-P30</f>
         <v>14816</v>
       </c>
       <c r="Q31" s="21">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>15808</v>
       </c>
       <c r="R31" s="21">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>11389</v>
       </c>
       <c r="S31" s="21">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>15814</v>
       </c>
       <c r="T31" s="21">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>18558</v>
       </c>
       <c r="U31" s="21">
@@ -3514,7 +3604,10 @@
         <f>V29-V30</f>
         <v>22344</v>
       </c>
-      <c r="W31" s="21"/>
+      <c r="W31" s="21">
+        <f>W29-W30</f>
+        <v>23222</v>
+      </c>
       <c r="X31" s="21"/>
       <c r="Y31" s="21"/>
       <c r="Z31" s="21"/>
@@ -3563,7 +3656,10 @@
         <f>8479-SUM(K32:L32)</f>
         <v>2895</v>
       </c>
-      <c r="N32" s="21"/>
+      <c r="N32" s="83">
+        <f>+W32-SUM(K32:M32)</f>
+        <v>3399</v>
+      </c>
       <c r="O32" s="21"/>
       <c r="P32" s="21">
         <v>9329</v>
@@ -3586,7 +3682,9 @@
       <c r="V32" s="21">
         <v>11555</v>
       </c>
-      <c r="W32" s="21"/>
+      <c r="W32" s="21">
+        <v>11878</v>
+      </c>
       <c r="X32" s="21"/>
       <c r="Y32" s="21"/>
       <c r="Z32" s="21"/>
@@ -3635,7 +3733,10 @@
         <f>-29-SUM(K33:L33)</f>
         <v>-24</v>
       </c>
-      <c r="N33" s="21"/>
+      <c r="N33" s="83">
+        <f>+W33-SUM(K33:M33)</f>
+        <v>-48</v>
+      </c>
       <c r="O33" s="21"/>
       <c r="P33" s="21">
         <v>-30</v>
@@ -3658,7 +3759,9 @@
       <c r="V33" s="21">
         <v>-60</v>
       </c>
-      <c r="W33" s="21"/>
+      <c r="W33" s="21">
+        <v>-77</v>
+      </c>
       <c r="X33" s="21"/>
       <c r="Y33" s="21"/>
       <c r="Z33" s="21"/>
@@ -3671,23 +3774,23 @@
         <v>25</v>
       </c>
       <c r="C34" s="21">
-        <f t="shared" ref="C34:J34" si="16">C31-C32+C33</f>
+        <f t="shared" ref="C34:J34" si="17">C31-C32+C33</f>
         <v>2195</v>
       </c>
       <c r="D34" s="21">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2467</v>
       </c>
       <c r="E34" s="21">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2766</v>
       </c>
       <c r="F34" s="21">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2420</v>
       </c>
       <c r="G34" s="21">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2370</v>
       </c>
       <c r="H34" s="21">
@@ -3695,45 +3798,48 @@
         <v>2670</v>
       </c>
       <c r="I34" s="21">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2926</v>
       </c>
       <c r="J34" s="21">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2762</v>
       </c>
       <c r="K34" s="21">
-        <f t="shared" ref="K34:M34" si="17">K31-K32+K33</f>
+        <f t="shared" ref="K34:N34" si="18">K31-K32+K33</f>
         <v>2394</v>
       </c>
       <c r="L34" s="21">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2720</v>
       </c>
       <c r="M34" s="21">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3188</v>
       </c>
-      <c r="N34" s="21"/>
+      <c r="N34" s="21">
+        <f t="shared" si="18"/>
+        <v>2965</v>
+      </c>
       <c r="O34" s="21"/>
       <c r="P34" s="21">
-        <f t="shared" ref="P34:T34" si="18">P31-P32+P33</f>
+        <f t="shared" ref="P34:T34" si="19">P31-P32+P33</f>
         <v>5457</v>
       </c>
       <c r="Q34" s="21">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>7599</v>
       </c>
       <c r="R34" s="21">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>4551</v>
       </c>
       <c r="S34" s="21">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>7183</v>
       </c>
       <c r="T34" s="21">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>8648</v>
       </c>
       <c r="U34" s="21">
@@ -3744,7 +3850,10 @@
         <f>V31-V32+V33</f>
         <v>10729</v>
       </c>
-      <c r="W34" s="21"/>
+      <c r="W34" s="21">
+        <f>W31-W32+W33</f>
+        <v>11267</v>
+      </c>
       <c r="X34" s="21"/>
       <c r="Y34" s="21"/>
       <c r="Z34" s="21"/>
@@ -3789,7 +3898,10 @@
       <c r="M35" s="21">
         <v>0</v>
       </c>
-      <c r="N35" s="21"/>
+      <c r="N35" s="83">
+        <f>+W35-SUM(K35:M35)</f>
+        <v>0</v>
+      </c>
       <c r="O35" s="21"/>
       <c r="P35" s="21">
         <v>0</v>
@@ -3812,7 +3924,9 @@
       <c r="V35" s="21">
         <v>0</v>
       </c>
-      <c r="W35" s="21"/>
+      <c r="W35" s="21">
+        <v>0</v>
+      </c>
       <c r="X35" s="21"/>
       <c r="Y35" s="21"/>
       <c r="Z35" s="21"/>
@@ -3860,7 +3974,10 @@
         <f>2359-SUM(K36:L36)</f>
         <v>817</v>
       </c>
-      <c r="N36" s="21"/>
+      <c r="N36" s="83">
+        <f>+W36-SUM(K36:M36)</f>
+        <v>911</v>
+      </c>
       <c r="O36" s="21"/>
       <c r="P36" s="21">
         <v>1100</v>
@@ -3883,7 +4000,9 @@
       <c r="V36" s="21">
         <v>3174</v>
       </c>
-      <c r="W36" s="21"/>
+      <c r="W36" s="21">
+        <v>3270</v>
+      </c>
       <c r="X36" s="21"/>
       <c r="Y36" s="21"/>
       <c r="Z36" s="21"/>
@@ -3896,69 +4015,72 @@
         <v>30</v>
       </c>
       <c r="C37" s="21">
-        <f t="shared" ref="C37:J37" si="19">C34+C35-C36</f>
+        <f t="shared" ref="C37:J37" si="20">C34+C35-C36</f>
         <v>1483</v>
       </c>
       <c r="D37" s="21">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1681</v>
       </c>
       <c r="E37" s="21">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>2027</v>
       </c>
       <c r="F37" s="21">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1616</v>
       </c>
       <c r="G37" s="21">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1636</v>
       </c>
       <c r="H37" s="21">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1905</v>
       </c>
       <c r="I37" s="21">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>2132</v>
       </c>
       <c r="J37" s="21">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1882</v>
       </c>
       <c r="K37" s="21">
-        <f t="shared" ref="K37:M37" si="20">K34+K35-K36</f>
+        <f t="shared" ref="K37:N37" si="21">K34+K35-K36</f>
         <v>1642</v>
       </c>
       <c r="L37" s="21">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1930</v>
       </c>
       <c r="M37" s="21">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>2371</v>
       </c>
-      <c r="N37" s="21"/>
+      <c r="N37" s="21">
+        <f t="shared" si="21"/>
+        <v>2054</v>
+      </c>
       <c r="O37" s="21"/>
       <c r="P37" s="21">
-        <f t="shared" ref="P37:T37" si="21">P34+P35-P36</f>
+        <f t="shared" ref="P37:T37" si="22">P34+P35-P36</f>
         <v>4357</v>
       </c>
       <c r="Q37" s="21">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>4773</v>
       </c>
       <c r="R37" s="21">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1506</v>
       </c>
       <c r="S37" s="21">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>4282</v>
       </c>
       <c r="T37" s="21">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>5518</v>
       </c>
       <c r="U37" s="21">
@@ -3969,7 +4091,10 @@
         <f>V34+V35-V36</f>
         <v>7555</v>
       </c>
-      <c r="W37" s="21"/>
+      <c r="W37" s="21">
+        <f>W34+W35-W36</f>
+        <v>7997</v>
+      </c>
       <c r="X37" s="21"/>
       <c r="Y37" s="21"/>
       <c r="Z37" s="21"/>
@@ -4018,7 +4143,10 @@
         <f>-49-SUM(K38:L38)</f>
         <v>-37</v>
       </c>
-      <c r="N38" s="21"/>
+      <c r="N38" s="83">
+        <f>+W38-SUM(K38:M38)</f>
+        <v>-31</v>
+      </c>
       <c r="O38" s="21"/>
       <c r="P38" s="21">
         <v>17</v>
@@ -4041,7 +4169,9 @@
       <c r="V38" s="21">
         <v>-77</v>
       </c>
-      <c r="W38" s="21"/>
+      <c r="W38" s="21">
+        <v>-80</v>
+      </c>
       <c r="X38" s="21"/>
       <c r="Y38" s="21"/>
       <c r="Z38" s="21"/>
@@ -4090,7 +4220,10 @@
         <f>69-SUM(K39:L39)</f>
         <v>27</v>
       </c>
-      <c r="N39" s="21"/>
+      <c r="N39" s="83">
+        <f>+W39-SUM(K39:M39)</f>
+        <v>33</v>
+      </c>
       <c r="O39" s="21"/>
       <c r="P39" s="21">
         <v>54</v>
@@ -4113,7 +4246,9 @@
       <c r="V39" s="21">
         <v>99</v>
       </c>
-      <c r="W39" s="21"/>
+      <c r="W39" s="21">
+        <v>102</v>
+      </c>
       <c r="X39" s="21"/>
       <c r="Y39" s="21"/>
       <c r="Z39" s="21"/>
@@ -4126,69 +4261,72 @@
         <v>33</v>
       </c>
       <c r="C40" s="21">
-        <f t="shared" ref="C40:J40" si="22">C37+C38+C39</f>
+        <f t="shared" ref="C40:J40" si="23">C37+C38+C39</f>
         <v>1505</v>
       </c>
       <c r="D40" s="21">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1747</v>
       </c>
       <c r="E40" s="21">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1985</v>
       </c>
       <c r="F40" s="21">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1631</v>
       </c>
       <c r="G40" s="21">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1671</v>
       </c>
       <c r="H40" s="21">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1927</v>
       </c>
       <c r="I40" s="21">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>2156</v>
       </c>
       <c r="J40" s="21">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1824</v>
       </c>
       <c r="K40" s="21">
-        <f t="shared" ref="K40:M40" si="23">K37+K38+K39</f>
+        <f t="shared" ref="K40:N40" si="24">K37+K38+K39</f>
         <v>1672</v>
       </c>
       <c r="L40" s="21">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1930</v>
       </c>
       <c r="M40" s="21">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>2361</v>
       </c>
-      <c r="N40" s="21"/>
+      <c r="N40" s="21">
+        <f t="shared" si="24"/>
+        <v>2056</v>
+      </c>
       <c r="O40" s="21"/>
       <c r="P40" s="21">
-        <f t="shared" ref="P40:T40" si="24">P37+P38+P39</f>
+        <f t="shared" ref="P40:T40" si="25">P37+P38+P39</f>
         <v>4428</v>
       </c>
       <c r="Q40" s="21">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>4682</v>
       </c>
       <c r="R40" s="21">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>1400</v>
       </c>
       <c r="S40" s="21">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>4198</v>
       </c>
       <c r="T40" s="21">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>5357</v>
       </c>
       <c r="U40" s="21">
@@ -4199,7 +4337,10 @@
         <f>V37+V38+V39</f>
         <v>7577</v>
       </c>
-      <c r="W40" s="21"/>
+      <c r="W40" s="21">
+        <f>W37+W38+W39</f>
+        <v>8019</v>
+      </c>
       <c r="X40" s="21"/>
       <c r="Y40" s="21"/>
       <c r="Z40" s="21"/>
@@ -4246,7 +4387,10 @@
         <f>1341-SUM(K41:L41)</f>
         <v>531</v>
       </c>
-      <c r="N41" s="21"/>
+      <c r="N41" s="83">
+        <f>+W41-SUM(K41:M41)</f>
+        <v>459</v>
+      </c>
       <c r="O41" s="21"/>
       <c r="P41" s="21">
         <v>980</v>
@@ -4269,7 +4413,9 @@
       <c r="V41" s="21">
         <v>1700</v>
       </c>
-      <c r="W41" s="21"/>
+      <c r="W41" s="21">
+        <v>1800</v>
+      </c>
       <c r="X41" s="21"/>
       <c r="Y41" s="21"/>
       <c r="Z41" s="21"/>
@@ -4282,69 +4428,72 @@
         <v>35</v>
       </c>
       <c r="C42" s="21">
-        <f t="shared" ref="C42:J42" si="25">C40-C41</f>
+        <f t="shared" ref="C42:J42" si="26">C40-C41</f>
         <v>1172</v>
       </c>
       <c r="D42" s="21">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1348</v>
       </c>
       <c r="E42" s="21">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1593</v>
       </c>
       <c r="F42" s="21">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1280</v>
       </c>
       <c r="G42" s="21">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1298</v>
       </c>
       <c r="H42" s="21">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1479</v>
       </c>
       <c r="I42" s="21">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1682</v>
       </c>
       <c r="J42" s="21">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1418</v>
       </c>
       <c r="K42" s="21">
-        <f t="shared" ref="K42:M42" si="26">K40-K41</f>
+        <f t="shared" ref="K42:N42" si="27">K40-K41</f>
         <v>1306</v>
       </c>
       <c r="L42" s="21">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>1486</v>
       </c>
       <c r="M42" s="21">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>1830</v>
       </c>
-      <c r="N42" s="21"/>
+      <c r="N42" s="21">
+        <f t="shared" si="27"/>
+        <v>1597</v>
+      </c>
       <c r="O42" s="21"/>
       <c r="P42" s="21">
-        <f t="shared" ref="P42:T42" si="27">P40-P41</f>
+        <f t="shared" ref="P42:T42" si="28">P40-P41</f>
         <v>3448</v>
       </c>
       <c r="Q42" s="21">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>3648</v>
       </c>
       <c r="R42" s="21">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>1103</v>
       </c>
       <c r="S42" s="21">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>3249</v>
       </c>
       <c r="T42" s="21">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>4146</v>
       </c>
       <c r="U42" s="21">
@@ -4355,7 +4504,10 @@
         <f>V40-V41</f>
         <v>5877</v>
       </c>
-      <c r="W42" s="21"/>
+      <c r="W42" s="21">
+        <f>W40-W41</f>
+        <v>6219</v>
+      </c>
       <c r="X42" s="28"/>
       <c r="Y42" s="21"/>
       <c r="Z42" s="21"/>
@@ -4400,7 +4552,10 @@
       <c r="M43" s="21">
         <v>0</v>
       </c>
-      <c r="N43" s="21"/>
+      <c r="N43" s="83">
+        <f>+W43-SUM(K43:M43)</f>
+        <v>0</v>
+      </c>
       <c r="O43" s="21"/>
       <c r="P43" s="21">
         <v>4</v>
@@ -4423,7 +4578,9 @@
       <c r="V43" s="21">
         <v>11</v>
       </c>
-      <c r="W43" s="21"/>
+      <c r="W43" s="21">
+        <v>0</v>
+      </c>
       <c r="X43" s="21"/>
       <c r="Y43" s="21"/>
       <c r="Z43" s="21"/>
@@ -4436,65 +4593,68 @@
         <v>37</v>
       </c>
       <c r="C44" s="21">
-        <f t="shared" ref="C44:J44" si="28">C42-C43</f>
+        <f t="shared" ref="C44:J44" si="29">C42-C43</f>
         <v>1168</v>
       </c>
       <c r="D44" s="21">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1345</v>
       </c>
       <c r="E44" s="21">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1588</v>
       </c>
       <c r="F44" s="21">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1278</v>
       </c>
       <c r="G44" s="21">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1293</v>
       </c>
       <c r="H44" s="21">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1474</v>
       </c>
       <c r="I44" s="21">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1681</v>
       </c>
       <c r="J44" s="21">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1418</v>
       </c>
       <c r="K44" s="21">
-        <f t="shared" ref="K44:M44" si="29">K42-K43</f>
+        <f t="shared" ref="K44:N44" si="30">K42-K43</f>
         <v>1306</v>
       </c>
       <c r="L44" s="21">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1486</v>
       </c>
       <c r="M44" s="21">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1830</v>
       </c>
-      <c r="N44" s="21"/>
+      <c r="N44" s="21">
+        <f t="shared" si="30"/>
+        <v>1597</v>
+      </c>
       <c r="O44" s="21"/>
       <c r="P44" s="21">
-        <f t="shared" ref="P44:S44" si="30">P42-P43</f>
+        <f t="shared" ref="P44:S44" si="31">P42-P43</f>
         <v>3444</v>
       </c>
       <c r="Q44" s="21">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>3640</v>
       </c>
       <c r="R44" s="21">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1105</v>
       </c>
       <c r="S44" s="21">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>3242</v>
       </c>
       <c r="T44" s="21">
@@ -4509,7 +4669,10 @@
         <f>V42-V43</f>
         <v>5866</v>
       </c>
-      <c r="W44" s="21"/>
+      <c r="W44" s="21">
+        <f>W42-W43</f>
+        <v>6219</v>
+      </c>
       <c r="X44" s="21"/>
       <c r="Y44" s="21"/>
       <c r="Z44" s="21"/>
@@ -4551,67 +4714,71 @@
         <v>38</v>
       </c>
       <c r="C46" s="3">
-        <f t="shared" ref="C46:L46" si="31">C44/C47</f>
+        <f t="shared" ref="C46:L46" si="32">C44/C47</f>
         <v>0.37522047202407066</v>
       </c>
       <c r="D46" s="3">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.43208179355511561</v>
       </c>
       <c r="E46" s="3">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.51014564175875354</v>
       </c>
       <c r="F46" s="3">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.41055801647839235</v>
       </c>
       <c r="G46" s="3">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.41528106837439188</v>
       </c>
       <c r="H46" s="3">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.47332237715124015</v>
       </c>
       <c r="I46" s="3">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.53975871249438667</v>
       </c>
       <c r="J46" s="3">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.45095283906809808</v>
       </c>
       <c r="K46" s="3">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.41922963299327271</v>
       </c>
       <c r="L46" s="3">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.47692228260726244</v>
       </c>
       <c r="M46" s="3">
-        <f t="shared" ref="M46" si="32">M44/M47</f>
+        <f t="shared" ref="M46:N46" si="33">M44/M47</f>
         <v>0.58729164123314104</v>
+      </c>
+      <c r="N46" s="3">
+        <f t="shared" si="33"/>
+        <v>0.51250099914428515</v>
       </c>
       <c r="P46" s="3">
         <f>P44/P47</f>
         <v>1.1060789241132536</v>
       </c>
       <c r="Q46" s="3">
-        <f t="shared" ref="Q46:T46" si="33">Q44/Q47</f>
+        <f t="shared" ref="Q46:T46" si="34">Q44/Q47</f>
         <v>1.1687703803030633</v>
       </c>
       <c r="R46" s="3">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0.35475144224142657</v>
       </c>
       <c r="S46" s="3">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>1.0412481436744843</v>
       </c>
       <c r="T46" s="3">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>1.3266053525994213</v>
       </c>
       <c r="U46" s="3">
@@ -4622,6 +4789,10 @@
         <f>V44/V47</f>
         <v>1.8655073018148542</v>
       </c>
+      <c r="W46" s="3">
+        <f>W44/W47</f>
+        <v>1.9957693886526668</v>
+      </c>
     </row>
     <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B47" s="3" t="s">
@@ -4661,7 +4832,9 @@
       <c r="M47" s="5">
         <v>3115.9987160000001</v>
       </c>
-      <c r="N47" s="5"/>
+      <c r="N47" s="5">
+        <v>3116.0914859999998</v>
+      </c>
       <c r="O47" s="5"/>
       <c r="P47" s="5">
         <v>3113.701857</v>
@@ -4684,34 +4857,41 @@
       <c r="V47" s="5">
         <v>3144.4529830000001</v>
       </c>
+      <c r="W47" s="5">
+        <v>3116.0914859999998</v>
+      </c>
     </row>
     <row r="49" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B49" s="3" t="s">
         <v>16</v>
       </c>
       <c r="Q49" s="29">
-        <f t="shared" ref="Q49:V54" si="34">Q22/P22-1</f>
+        <f t="shared" ref="Q49:W54" si="35">Q22/P22-1</f>
         <v>8.562232950446691E-2</v>
       </c>
       <c r="R49" s="29">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>-0.27780617460641999</v>
       </c>
       <c r="S49" s="29">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.3862269091938566</v>
       </c>
       <c r="T49" s="29">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.21316246298376385</v>
       </c>
       <c r="U49" s="29">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>9.6334329363242377E-2</v>
       </c>
       <c r="V49" s="29">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>6.6333973128598789E-2</v>
+      </c>
+      <c r="W49" s="29">
+        <f t="shared" si="35"/>
+        <v>9.827921376629023E-3</v>
       </c>
     </row>
     <row r="50" spans="2:40" x14ac:dyDescent="0.2">
@@ -4719,28 +4899,32 @@
         <v>17</v>
       </c>
       <c r="Q50" s="29">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>5.8002148227712214E-2</v>
       </c>
       <c r="R50" s="29">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>-0.2766497461928934</v>
       </c>
       <c r="S50" s="29">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.31649122807017549</v>
       </c>
       <c r="T50" s="29">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.14712153518123672</v>
       </c>
       <c r="U50" s="29">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>9.6189591078067016E-2</v>
       </c>
       <c r="V50" s="29">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>4.6629927935565973E-2</v>
+      </c>
+      <c r="W50" s="29">
+        <f t="shared" si="35"/>
+        <v>3.1186715269339915E-2</v>
       </c>
     </row>
     <row r="51" spans="2:40" x14ac:dyDescent="0.2">
@@ -4748,28 +4932,32 @@
         <v>18</v>
       </c>
       <c r="Q51" s="29">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>5.4384017758046577E-2</v>
       </c>
       <c r="R51" s="29">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>-0.33105263157894738</v>
       </c>
       <c r="S51" s="29">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.30055074744295829</v>
       </c>
       <c r="T51" s="29">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>-3.6297640653357499E-2</v>
       </c>
       <c r="U51" s="29">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.15442561205273075</v>
       </c>
       <c r="V51" s="29">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>6.579662860250135E-2</v>
+      </c>
+      <c r="W51" s="29">
+        <f t="shared" si="35"/>
+        <v>3.0102040816326614E-2</v>
       </c>
     </row>
     <row r="52" spans="2:40" x14ac:dyDescent="0.2">
@@ -4777,28 +4965,32 @@
         <v>19</v>
       </c>
       <c r="Q52" s="29">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>6.4285714285714279E-2</v>
       </c>
       <c r="R52" s="29">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>-0.25671140939597314</v>
       </c>
       <c r="S52" s="29">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.22855530474040631</v>
       </c>
       <c r="T52" s="29">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>9.5084979329352226E-2</v>
       </c>
       <c r="U52" s="29">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>9.941275167785224E-2</v>
       </c>
       <c r="V52" s="29">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.11789393361312483</v>
+      </c>
+      <c r="W52" s="29">
+        <f t="shared" si="35"/>
+        <v>0.12150170648464154</v>
       </c>
     </row>
     <row r="53" spans="2:40" x14ac:dyDescent="0.2">
@@ -4806,28 +4998,32 @@
         <v>20</v>
       </c>
       <c r="Q53" s="29">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.14080834419817467</v>
       </c>
       <c r="R53" s="29">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>-0.2668571428571429</v>
       </c>
       <c r="S53" s="29">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.42166796570537812</v>
       </c>
       <c r="T53" s="29">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.12719298245614041</v>
       </c>
       <c r="U53" s="29">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.13521400778210113</v>
       </c>
       <c r="V53" s="29">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.1413881748071979</v>
+      </c>
+      <c r="W53" s="29">
+        <f t="shared" si="35"/>
+        <v>0.12687687687687688</v>
       </c>
     </row>
     <row r="54" spans="2:40" x14ac:dyDescent="0.2">
@@ -4835,28 +5031,32 @@
         <v>21</v>
       </c>
       <c r="Q54" s="29">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>3.2478632478632585E-2</v>
       </c>
       <c r="R54" s="29">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>-0.13576158940397354</v>
       </c>
       <c r="S54" s="29">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.14942528735632177</v>
       </c>
       <c r="T54" s="29">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>3.833333333333333E-2</v>
       </c>
       <c r="U54" s="29">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.1942215088282504</v>
       </c>
       <c r="V54" s="29">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.11693548387096775</v>
+      </c>
+      <c r="W54" s="29">
+        <f t="shared" si="35"/>
+        <v>0.15523465703971118</v>
       </c>
     </row>
     <row r="55" spans="2:40" x14ac:dyDescent="0.2">
@@ -4868,59 +5068,63 @@
       <c r="E55" s="27"/>
       <c r="F55" s="27"/>
       <c r="G55" s="30">
-        <f t="shared" ref="G55:M55" si="35">G29/C29-1</f>
+        <f t="shared" ref="G55:M55" si="36">G29/C29-1</f>
         <v>7.0818552095651022E-2</v>
       </c>
       <c r="H55" s="30">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>7.3168091784825195E-2</v>
       </c>
       <c r="I55" s="30">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>6.839461064169905E-2</v>
       </c>
       <c r="J55" s="30">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>8.434900367575926E-2</v>
       </c>
       <c r="K55" s="30">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1.5214723926380458E-2</v>
       </c>
       <c r="L55" s="30">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1.6944024205748809E-2</v>
       </c>
       <c r="M55" s="30">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>4.8840440312065914E-2</v>
       </c>
       <c r="N55" s="30"/>
       <c r="O55" s="27"/>
       <c r="P55" s="27"/>
       <c r="Q55" s="30">
-        <f t="shared" ref="Q55:V55" si="36">Q29/P29-1</f>
+        <f t="shared" ref="Q55:W55" si="37">Q29/P29-1</f>
         <v>8.192771084337358E-2</v>
       </c>
       <c r="R55" s="30">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>-0.27874995581008943</v>
       </c>
       <c r="S55" s="30">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0.3584942652681109</v>
       </c>
       <c r="T55" s="30">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0.17509741665463996</v>
       </c>
       <c r="U55" s="30">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0.10371825969480186</v>
       </c>
       <c r="V55" s="30">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>7.4693298467187752E-2</v>
+      </c>
+      <c r="W55" s="30">
+        <f t="shared" si="37"/>
+        <v>3.1890660592255093E-2</v>
       </c>
     </row>
     <row r="56" spans="2:40" x14ac:dyDescent="0.2">
@@ -4928,77 +5132,81 @@
         <v>62</v>
       </c>
       <c r="C56" s="29">
-        <f t="shared" ref="C56:J56" si="37">C31/C29</f>
+        <f t="shared" ref="C56:J56" si="38">C31/C29</f>
         <v>0.60478255157009586</v>
       </c>
       <c r="D56" s="29">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.56250676480138539</v>
       </c>
       <c r="E56" s="29">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.61680749029458781</v>
       </c>
       <c r="F56" s="29">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.53762816792416324</v>
       </c>
       <c r="G56" s="29">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.60613496932515343</v>
       </c>
       <c r="H56" s="29">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.56490166414523446</v>
       </c>
       <c r="I56" s="29">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.61440632681414986</v>
       </c>
       <c r="J56" s="29">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.53996431757359498</v>
       </c>
       <c r="K56" s="29">
-        <f t="shared" ref="K56:L56" si="38">K31/K29</f>
+        <f t="shared" ref="K56:L56" si="39">K31/K29</f>
         <v>0.60575296108291032</v>
       </c>
       <c r="L56" s="29">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0.56441535257363884</v>
       </c>
       <c r="M56" s="29">
-        <f t="shared" ref="M56" si="39">M31/M29</f>
+        <f t="shared" ref="M56" si="40">M31/M29</f>
         <v>0.62227430201752598</v>
       </c>
       <c r="N56" s="29"/>
       <c r="P56" s="29">
-        <f t="shared" ref="P56:V56" si="40">P31/P29</f>
+        <f t="shared" ref="P56:V56" si="41">P31/P29</f>
         <v>0.56668579078217629</v>
       </c>
       <c r="Q56" s="29">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.55884328490119139</v>
       </c>
       <c r="R56" s="29">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.55822958533477107</v>
       </c>
       <c r="S56" s="29">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.57057295425025256</v>
       </c>
       <c r="T56" s="29">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.56980564340323625</v>
       </c>
       <c r="U56" s="29">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.57754471861351431</v>
       </c>
       <c r="V56" s="29">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.57838061710499067</v>
+      </c>
+      <c r="W56" s="29">
+        <f t="shared" ref="W56" si="42">W31/W29</f>
+        <v>0.58253060405378287</v>
       </c>
     </row>
     <row r="57" spans="2:40" x14ac:dyDescent="0.2">
@@ -5006,77 +5214,81 @@
         <v>63</v>
       </c>
       <c r="C57" s="29">
-        <f t="shared" ref="C57:J57" si="41">C34/C29</f>
+        <f t="shared" ref="C57:J57" si="43">C34/C29</f>
         <v>0.28839837077913544</v>
       </c>
       <c r="D57" s="29">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0.26702024028574523</v>
       </c>
       <c r="E57" s="29">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0.3158255309431377</v>
       </c>
       <c r="F57" s="29">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0.23408783130199265</v>
       </c>
       <c r="G57" s="29">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0.29079754601226993</v>
       </c>
       <c r="H57" s="29">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0.2692889561270802</v>
       </c>
       <c r="I57" s="29">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0.31270706422998823</v>
       </c>
       <c r="J57" s="29">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0.24638715432649419</v>
       </c>
       <c r="K57" s="29">
-        <f t="shared" ref="K57:L57" si="42">K34/K29</f>
+        <f t="shared" ref="K57:L57" si="44">K34/K29</f>
         <v>0.28934010152284262</v>
       </c>
       <c r="L57" s="29">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0.26976098383417635</v>
       </c>
       <c r="M57" s="29">
-        <f t="shared" ref="M57" si="43">M34/M29</f>
+        <f t="shared" ref="M57" si="45">M34/M29</f>
         <v>0.32484206235989405</v>
       </c>
       <c r="N57" s="29"/>
       <c r="P57" s="29">
-        <f t="shared" ref="P57:V57" si="44">P34/P29</f>
+        <f t="shared" ref="P57:V57" si="46">P34/P29</f>
         <v>0.20872059667240389</v>
       </c>
       <c r="Q57" s="29">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>0.26863930427404814</v>
       </c>
       <c r="R57" s="29">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>0.22306636604254484</v>
       </c>
       <c r="S57" s="29">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>0.25916438158464422</v>
       </c>
       <c r="T57" s="29">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>0.26552857011268383</v>
       </c>
       <c r="U57" s="29">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>0.27398670264556152</v>
       </c>
       <c r="V57" s="29">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>0.27772313108303998</v>
+      </c>
+      <c r="W57" s="29">
+        <f t="shared" ref="W57" si="47">W34/W29</f>
+        <v>0.28263596227172388</v>
       </c>
     </row>
     <row r="58" spans="2:40" x14ac:dyDescent="0.2">
@@ -5084,77 +5296,81 @@
         <v>64</v>
       </c>
       <c r="C58" s="29">
-        <f t="shared" ref="C58:J58" si="45">C37/C29</f>
+        <f t="shared" ref="C58:J58" si="48">C37/C29</f>
         <v>0.194849559847589</v>
       </c>
       <c r="D58" s="29">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>0.18194609806256087</v>
       </c>
       <c r="E58" s="29">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>0.23144553551039049</v>
       </c>
       <c r="F58" s="29">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>0.1563165022248017</v>
       </c>
       <c r="G58" s="29">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>0.2007361963190184</v>
       </c>
       <c r="H58" s="29">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>0.19213313161875945</v>
       </c>
       <c r="I58" s="29">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>0.22785080688254783</v>
       </c>
       <c r="J58" s="29">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>0.16788581623550403</v>
       </c>
       <c r="K58" s="29">
-        <f t="shared" ref="K58:L58" si="46">K37/K29</f>
+        <f t="shared" ref="K58:L58" si="49">K37/K29</f>
         <v>0.1984529852550157</v>
       </c>
       <c r="L58" s="29">
-        <f t="shared" si="46"/>
+        <f t="shared" si="49"/>
         <v>0.19141128632351484</v>
       </c>
       <c r="M58" s="29">
-        <f t="shared" ref="M58" si="47">M37/M29</f>
+        <f t="shared" ref="M58" si="50">M37/M29</f>
         <v>0.24159364173629508</v>
       </c>
       <c r="N58" s="29"/>
       <c r="P58" s="29">
-        <f t="shared" ref="P58:V58" si="48">P37/P29</f>
+        <f t="shared" ref="P58:V58" si="51">P37/P29</f>
         <v>0.16664754255115702</v>
       </c>
       <c r="Q58" s="29">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>0.16873475448085692</v>
       </c>
       <c r="R58" s="29">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>7.3816292520341137E-2</v>
       </c>
       <c r="S58" s="29">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>0.15449559821041997</v>
       </c>
       <c r="T58" s="29">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>0.16942491326107648</v>
       </c>
       <c r="U58" s="29">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>0.18938993518235181</v>
       </c>
       <c r="V58" s="29">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>0.1955632636156554</v>
+      </c>
+      <c r="W58" s="29">
+        <f t="shared" ref="W58" si="52">W37/W29</f>
+        <v>0.20060706401766004</v>
       </c>
     </row>
     <row r="59" spans="2:40" x14ac:dyDescent="0.2">
@@ -5162,77 +5378,81 @@
         <v>65</v>
       </c>
       <c r="C59" s="29">
-        <f t="shared" ref="C59:J59" si="49">C42/C29</f>
+        <f t="shared" ref="C59:J59" si="53">C42/C29</f>
         <v>0.15398764945473656</v>
       </c>
       <c r="D59" s="29">
-        <f t="shared" si="49"/>
+        <f t="shared" si="53"/>
         <v>0.14590323628098278</v>
       </c>
       <c r="E59" s="29">
-        <f t="shared" si="49"/>
+        <f t="shared" si="53"/>
         <v>0.18189084265814112</v>
       </c>
       <c r="F59" s="29">
-        <f t="shared" si="49"/>
+        <f t="shared" si="53"/>
         <v>0.12381505126716967</v>
       </c>
       <c r="G59" s="29">
-        <f t="shared" si="49"/>
+        <f t="shared" si="53"/>
         <v>0.15926380368098159</v>
       </c>
       <c r="H59" s="29">
-        <f t="shared" si="49"/>
+        <f t="shared" si="53"/>
         <v>0.14916792738275339</v>
       </c>
       <c r="I59" s="29">
-        <f t="shared" si="49"/>
+        <f t="shared" si="53"/>
         <v>0.17975846959495564</v>
       </c>
       <c r="J59" s="29">
-        <f t="shared" si="49"/>
+        <f t="shared" si="53"/>
         <v>0.12649420160570918</v>
       </c>
       <c r="K59" s="29">
-        <f t="shared" ref="K59:L59" si="50">K42/K29</f>
+        <f t="shared" ref="K59:L59" si="54">K42/K29</f>
         <v>0.15784384819917816</v>
       </c>
       <c r="L59" s="29">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v>0.14737677278587721</v>
       </c>
       <c r="M59" s="29">
-        <f t="shared" ref="M59" si="51">M42/M29</f>
+        <f t="shared" ref="M59" si="55">M42/M29</f>
         <v>0.18646831057672714</v>
       </c>
       <c r="N59" s="29"/>
       <c r="P59" s="29">
-        <f t="shared" ref="P59:V59" si="52">P42/P29</f>
+        <f t="shared" ref="P59:V59" si="56">P42/P29</f>
         <v>0.13187990055459936</v>
       </c>
       <c r="Q59" s="29">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>0.12896383497719802</v>
       </c>
       <c r="R59" s="29">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>5.4063327124791685E-2</v>
       </c>
       <c r="S59" s="29">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>0.11722470775003609</v>
       </c>
       <c r="T59" s="29">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>0.12729896527372656</v>
       </c>
       <c r="U59" s="29">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>0.15005424652961305</v>
       </c>
       <c r="V59" s="29">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>0.15212776972458067</v>
+      </c>
+      <c r="W59" s="29">
+        <f t="shared" ref="W59" si="57">W42/W29</f>
+        <v>0.15600541842263696</v>
       </c>
     </row>
     <row r="60" spans="2:40" x14ac:dyDescent="0.2">
@@ -5256,28 +5476,32 @@
       <c r="N60" s="29"/>
       <c r="P60" s="29"/>
       <c r="Q60" s="29">
-        <f t="shared" ref="Q60:V60" si="53">(Q34-P34)/(Q29-P29)</f>
+        <f t="shared" ref="Q60:W60" si="58">(Q34-P34)/(Q29-P29)</f>
         <v>1</v>
       </c>
       <c r="R60" s="29">
-        <f t="shared" si="53"/>
+        <f t="shared" si="58"/>
         <v>0.38655675332910588</v>
       </c>
       <c r="S60" s="29">
-        <f t="shared" si="53"/>
+        <f t="shared" si="58"/>
         <v>0.35985780694558384</v>
       </c>
       <c r="T60" s="29">
-        <f t="shared" si="53"/>
+        <f t="shared" si="58"/>
         <v>0.30187512878631773</v>
       </c>
       <c r="U60" s="29">
-        <f t="shared" si="53"/>
+        <f t="shared" si="58"/>
         <v>0.35553582001184131</v>
       </c>
       <c r="V60" s="29">
-        <f t="shared" si="53"/>
+        <f t="shared" si="58"/>
         <v>0.32774674115456237</v>
+      </c>
+      <c r="W60" s="29">
+        <f t="shared" si="58"/>
+        <v>0.43668831168831168</v>
       </c>
     </row>
     <row r="61" spans="2:40" x14ac:dyDescent="0.2">
@@ -5285,80 +5509,81 @@
         <v>66</v>
       </c>
       <c r="C61" s="29">
-        <f t="shared" ref="C61:M61" si="54">C41/C40</f>
+        <f t="shared" ref="C61:M61" si="59">C41/C40</f>
         <v>0.22126245847176079</v>
       </c>
       <c r="D61" s="29">
-        <f t="shared" si="54"/>
+        <f t="shared" si="59"/>
         <v>0.22839152833428736</v>
       </c>
       <c r="E61" s="29">
-        <f t="shared" si="54"/>
+        <f t="shared" si="59"/>
         <v>0.19748110831234256</v>
       </c>
       <c r="F61" s="29">
-        <f t="shared" si="54"/>
+        <f t="shared" si="59"/>
         <v>0.21520539546290618</v>
       </c>
       <c r="G61" s="29">
-        <f t="shared" si="54"/>
+        <f t="shared" si="59"/>
         <v>0.2232196289646918</v>
       </c>
       <c r="H61" s="29">
-        <f t="shared" si="54"/>
+        <f t="shared" si="59"/>
         <v>0.23248572911261028</v>
       </c>
       <c r="I61" s="29">
-        <f t="shared" si="54"/>
+        <f t="shared" si="59"/>
         <v>0.21985157699443414</v>
       </c>
       <c r="J61" s="29">
-        <f t="shared" si="54"/>
+        <f t="shared" si="59"/>
         <v>0.22258771929824561</v>
       </c>
       <c r="K61" s="29">
-        <f t="shared" si="54"/>
+        <f t="shared" si="59"/>
         <v>0.21889952153110048</v>
       </c>
       <c r="L61" s="29">
-        <f t="shared" si="54"/>
+        <f t="shared" si="59"/>
         <v>0.23005181347150258</v>
       </c>
       <c r="M61" s="29">
-        <f t="shared" si="54"/>
+        <f t="shared" si="59"/>
         <v>0.22490470139771285</v>
       </c>
       <c r="N61" s="29"/>
       <c r="P61" s="29">
-        <f t="shared" ref="P61:V61" si="55">P41/P40</f>
+        <f t="shared" ref="P61:V61" si="60">P41/P40</f>
         <v>0.22131887985546522</v>
       </c>
       <c r="Q61" s="29">
-        <f t="shared" si="55"/>
+        <f t="shared" si="60"/>
         <v>0.22084579239641178</v>
       </c>
       <c r="R61" s="29">
-        <f t="shared" si="55"/>
+        <f t="shared" si="60"/>
         <v>0.21214285714285713</v>
       </c>
       <c r="S61" s="29">
-        <f t="shared" si="55"/>
+        <f t="shared" si="60"/>
         <v>0.22606002858504048</v>
       </c>
       <c r="T61" s="29">
-        <f t="shared" si="55"/>
+        <f t="shared" si="60"/>
         <v>0.22605936158297554</v>
       </c>
       <c r="U61" s="29">
-        <f t="shared" si="55"/>
+        <f t="shared" si="60"/>
         <v>0.21473285776677828</v>
       </c>
       <c r="V61" s="29">
-        <f t="shared" si="55"/>
+        <f t="shared" si="60"/>
         <v>0.22436320443447275</v>
       </c>
-      <c r="W61" s="31">
-        <v>0.25</v>
+      <c r="W61" s="29">
+        <f t="shared" ref="W61" si="61">W41/W40</f>
+        <v>0.22446689113355781</v>
       </c>
     </row>
     <row r="63" spans="2:40" x14ac:dyDescent="0.2">
@@ -5403,7 +5628,9 @@
       <c r="V63" s="21">
         <v>5269</v>
       </c>
-      <c r="W63" s="21"/>
+      <c r="W63" s="21">
+        <v>5542</v>
+      </c>
       <c r="X63" s="21"/>
       <c r="Y63" s="21"/>
       <c r="Z63" s="21"/>
@@ -5464,7 +5691,9 @@
       <c r="V64" s="21">
         <v>1607</v>
       </c>
-      <c r="W64" s="21"/>
+      <c r="W64" s="21">
+        <v>1840</v>
+      </c>
       <c r="X64" s="21"/>
       <c r="Y64" s="21"/>
       <c r="Z64" s="21"/>
@@ -5525,7 +5754,9 @@
       <c r="V65" s="21">
         <v>10014</v>
       </c>
-      <c r="W65" s="21"/>
+      <c r="W65" s="21">
+        <v>11142</v>
+      </c>
       <c r="X65" s="21"/>
       <c r="Y65" s="21"/>
       <c r="Z65" s="21"/>
@@ -5586,7 +5817,9 @@
       <c r="V66" s="21">
         <v>450</v>
       </c>
-      <c r="W66" s="21"/>
+      <c r="W66" s="21">
+        <v>471</v>
+      </c>
       <c r="X66" s="21"/>
       <c r="Y66" s="21"/>
       <c r="Z66" s="21"/>
@@ -5647,7 +5880,9 @@
       <c r="V67" s="21">
         <v>1017</v>
       </c>
-      <c r="W67" s="21"/>
+      <c r="W67" s="21">
+        <v>952</v>
+      </c>
       <c r="X67" s="21"/>
       <c r="Y67" s="21"/>
       <c r="Z67" s="21"/>
@@ -5671,35 +5906,35 @@
         <v>44</v>
       </c>
       <c r="C68" s="21">
-        <f t="shared" ref="C68:J68" si="56">SUM(C63:C67)</f>
+        <f t="shared" ref="C68:J68" si="62">SUM(C63:C67)</f>
         <v>0</v>
       </c>
       <c r="D68" s="21">
-        <f t="shared" si="56"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="E68" s="21">
-        <f t="shared" si="56"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="F68" s="21">
-        <f t="shared" si="56"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="G68" s="21">
-        <f t="shared" si="56"/>
+        <f t="shared" si="62"/>
         <v>16891</v>
       </c>
       <c r="H68" s="21">
-        <f t="shared" si="56"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="I68" s="21">
-        <f t="shared" si="56"/>
+        <f t="shared" si="62"/>
         <v>17992</v>
       </c>
       <c r="J68" s="21">
-        <f t="shared" si="56"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="K68" s="21"/>
@@ -5708,34 +5943,37 @@
       <c r="N68" s="21"/>
       <c r="O68" s="21"/>
       <c r="P68" s="21">
-        <f t="shared" ref="P68:V68" si="57">SUM(P63:P67)</f>
+        <f t="shared" ref="P68:W68" si="63">SUM(P63:P67)</f>
         <v>11064</v>
       </c>
       <c r="Q68" s="21">
-        <f t="shared" si="57"/>
+        <f t="shared" si="63"/>
         <v>16978</v>
       </c>
       <c r="R68" s="21">
-        <f t="shared" si="57"/>
+        <f t="shared" si="63"/>
         <v>15461</v>
       </c>
       <c r="S68" s="21">
-        <f t="shared" si="57"/>
+        <f t="shared" si="63"/>
         <v>15343</v>
       </c>
       <c r="T68" s="21">
-        <f t="shared" si="57"/>
+        <f t="shared" si="63"/>
         <v>15344</v>
       </c>
       <c r="U68" s="21">
-        <f t="shared" si="57"/>
+        <f t="shared" si="63"/>
         <v>16719</v>
       </c>
       <c r="V68" s="21">
-        <f t="shared" si="57"/>
+        <f t="shared" si="63"/>
         <v>18357</v>
       </c>
-      <c r="W68" s="21"/>
+      <c r="W68" s="21">
+        <f t="shared" si="63"/>
+        <v>19947</v>
+      </c>
       <c r="X68" s="21"/>
       <c r="Y68" s="21"/>
       <c r="Z68" s="21"/>
@@ -5796,7 +6034,9 @@
       <c r="V69" s="21">
         <v>3321</v>
       </c>
-      <c r="W69" s="21"/>
+      <c r="W69" s="21">
+        <v>3249</v>
+      </c>
       <c r="X69" s="21"/>
       <c r="Y69" s="21"/>
       <c r="Z69" s="21"/>
@@ -5857,7 +6097,9 @@
       <c r="V70" s="21">
         <v>1088</v>
       </c>
-      <c r="W70" s="21"/>
+      <c r="W70" s="21">
+        <v>1166</v>
+      </c>
       <c r="X70" s="21"/>
       <c r="Y70" s="21"/>
       <c r="Z70" s="21"/>
@@ -5918,7 +6160,9 @@
       <c r="V71" s="21">
         <v>5120</v>
       </c>
-      <c r="W71" s="21"/>
+      <c r="W71" s="21">
+        <v>5684</v>
+      </c>
       <c r="X71" s="21"/>
       <c r="Y71" s="21"/>
       <c r="Z71" s="21"/>
@@ -5979,7 +6223,9 @@
       <c r="V72" s="21">
         <v>6382</v>
       </c>
-      <c r="W72" s="21"/>
+      <c r="W72" s="21">
+        <v>5276</v>
+      </c>
       <c r="X72" s="21"/>
       <c r="Y72" s="21"/>
       <c r="Z72" s="21"/>
@@ -6040,7 +6286,9 @@
       <c r="V73" s="21">
         <v>445</v>
       </c>
-      <c r="W73" s="21"/>
+      <c r="W73" s="21">
+        <v>316</v>
+      </c>
       <c r="X73" s="21"/>
       <c r="Y73" s="21"/>
       <c r="Z73" s="21"/>
@@ -6064,35 +6312,35 @@
         <v>50</v>
       </c>
       <c r="C74" s="21">
-        <f t="shared" ref="C74:J74" si="58">SUM(C69:C73)</f>
+        <f t="shared" ref="C74:J74" si="64">SUM(C69:C73)</f>
         <v>0</v>
       </c>
       <c r="D74" s="21">
-        <f t="shared" si="58"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="E74" s="21">
-        <f t="shared" si="58"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="F74" s="21">
-        <f t="shared" si="58"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="G74" s="21">
-        <f t="shared" si="58"/>
+        <f t="shared" si="64"/>
         <v>17079</v>
       </c>
       <c r="H74" s="21">
-        <f t="shared" si="58"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="I74" s="21">
-        <f t="shared" si="58"/>
+        <f t="shared" si="64"/>
         <v>18099</v>
       </c>
       <c r="J74" s="21">
-        <f t="shared" si="58"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="K74" s="21"/>
@@ -6101,23 +6349,23 @@
       <c r="N74" s="21"/>
       <c r="O74" s="21"/>
       <c r="P74" s="21">
-        <f t="shared" ref="P74:T74" si="59">SUM(P69:P73)</f>
+        <f t="shared" ref="P74:T74" si="65">SUM(P69:P73)</f>
         <v>10620</v>
       </c>
       <c r="Q74" s="21">
-        <f t="shared" si="59"/>
+        <f t="shared" si="65"/>
         <v>11413</v>
       </c>
       <c r="R74" s="21">
-        <f t="shared" si="59"/>
+        <f t="shared" si="65"/>
         <v>10957</v>
       </c>
       <c r="S74" s="21">
-        <f t="shared" si="59"/>
+        <f t="shared" si="65"/>
         <v>13602</v>
       </c>
       <c r="T74" s="21">
-        <f t="shared" si="59"/>
+        <f t="shared" si="65"/>
         <v>14640</v>
       </c>
       <c r="U74" s="21">
@@ -6128,7 +6376,10 @@
         <f>SUM(V69:V73)</f>
         <v>16356</v>
       </c>
-      <c r="W74" s="21"/>
+      <c r="W74" s="21">
+        <f>SUM(W69:W73)</f>
+        <v>15691</v>
+      </c>
       <c r="X74" s="21"/>
       <c r="Y74" s="21"/>
       <c r="Z74" s="21"/>
@@ -6152,35 +6403,35 @@
         <v>49</v>
       </c>
       <c r="C75" s="28">
-        <f t="shared" ref="C75:J75" si="60">C68+C74</f>
+        <f t="shared" ref="C75:J75" si="66">C68+C74</f>
         <v>0</v>
       </c>
       <c r="D75" s="28">
-        <f t="shared" si="60"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="E75" s="28">
-        <f t="shared" si="60"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="F75" s="28">
-        <f t="shared" si="60"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="G75" s="28">
-        <f t="shared" si="60"/>
+        <f t="shared" si="66"/>
         <v>33970</v>
       </c>
       <c r="H75" s="28">
-        <f t="shared" si="60"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="I75" s="28">
-        <f t="shared" si="60"/>
+        <f t="shared" si="66"/>
         <v>36091</v>
       </c>
       <c r="J75" s="28">
-        <f t="shared" si="60"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="K75" s="28"/>
@@ -6189,34 +6440,37 @@
       <c r="N75" s="28"/>
       <c r="O75" s="28"/>
       <c r="P75" s="28">
-        <f t="shared" ref="P75:V75" si="61">P68+P74</f>
+        <f t="shared" ref="P75:W75" si="67">P68+P74</f>
         <v>21684</v>
       </c>
       <c r="Q75" s="28">
-        <f t="shared" si="61"/>
+        <f t="shared" si="67"/>
         <v>28391</v>
       </c>
       <c r="R75" s="28">
-        <f t="shared" si="61"/>
+        <f t="shared" si="67"/>
         <v>26418</v>
       </c>
       <c r="S75" s="28">
-        <f t="shared" si="61"/>
+        <f t="shared" si="67"/>
         <v>28945</v>
       </c>
       <c r="T75" s="28">
-        <f t="shared" si="61"/>
+        <f t="shared" si="67"/>
         <v>29984</v>
       </c>
       <c r="U75" s="28">
-        <f t="shared" si="61"/>
+        <f t="shared" si="67"/>
         <v>32735</v>
       </c>
       <c r="V75" s="28">
-        <f t="shared" si="61"/>
+        <f t="shared" si="67"/>
         <v>34713</v>
       </c>
-      <c r="W75" s="21"/>
+      <c r="W75" s="28">
+        <f t="shared" si="67"/>
+        <v>35638</v>
+      </c>
       <c r="X75" s="21"/>
       <c r="Y75" s="21"/>
       <c r="Z75" s="21"/>
@@ -6318,7 +6572,9 @@
       <c r="V77" s="21">
         <v>19676</v>
       </c>
-      <c r="W77" s="21"/>
+      <c r="W77" s="21">
+        <v>20395</v>
+      </c>
       <c r="X77" s="21"/>
       <c r="Y77" s="21"/>
       <c r="Z77" s="21"/>
@@ -6379,7 +6635,9 @@
       <c r="V78" s="21">
         <v>0</v>
       </c>
-      <c r="W78" s="21"/>
+      <c r="W78" s="21">
+        <v>0</v>
+      </c>
       <c r="X78" s="21"/>
       <c r="Y78" s="21"/>
       <c r="Z78" s="21"/>
@@ -6403,35 +6661,35 @@
         <v>53</v>
       </c>
       <c r="C79" s="28">
-        <f t="shared" ref="C79:J79" si="62">C77+C78</f>
+        <f t="shared" ref="C79:J79" si="68">C77+C78</f>
         <v>0</v>
       </c>
       <c r="D79" s="28">
-        <f t="shared" si="62"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="E79" s="28">
-        <f t="shared" si="62"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="F79" s="28">
-        <f t="shared" si="62"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="G79" s="28">
-        <f t="shared" si="62"/>
+        <f t="shared" si="68"/>
         <v>17554</v>
       </c>
       <c r="H79" s="28">
-        <f t="shared" si="62"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="I79" s="28">
-        <f t="shared" si="62"/>
+        <f t="shared" si="68"/>
         <v>18140</v>
       </c>
       <c r="J79" s="28">
-        <f t="shared" si="62"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="K79" s="28"/>
@@ -6440,23 +6698,23 @@
       <c r="N79" s="28"/>
       <c r="O79" s="28"/>
       <c r="P79" s="28">
-        <f t="shared" ref="P79:T79" si="63">P77+P78</f>
+        <f t="shared" ref="P79:T79" si="69">P77+P78</f>
         <v>14683</v>
       </c>
       <c r="Q79" s="28">
-        <f t="shared" si="63"/>
+        <f t="shared" si="69"/>
         <v>14949</v>
       </c>
       <c r="R79" s="28">
-        <f t="shared" si="63"/>
+        <f t="shared" si="69"/>
         <v>14550</v>
       </c>
       <c r="S79" s="28">
-        <f t="shared" si="63"/>
+        <f t="shared" si="69"/>
         <v>15759</v>
       </c>
       <c r="T79" s="28">
-        <f t="shared" si="63"/>
+        <f t="shared" si="69"/>
         <v>17033</v>
       </c>
       <c r="U79" s="28">
@@ -6467,7 +6725,10 @@
         <f>V77+V78</f>
         <v>19676</v>
       </c>
-      <c r="W79" s="21"/>
+      <c r="W79" s="28">
+        <f>W77+W78</f>
+        <v>20395</v>
+      </c>
       <c r="X79" s="21"/>
       <c r="Y79" s="21"/>
       <c r="Z79" s="21"/>
@@ -6528,7 +6789,9 @@
       <c r="V80" s="21">
         <v>72</v>
       </c>
-      <c r="W80" s="21"/>
+      <c r="W80" s="21">
+        <v>101</v>
+      </c>
       <c r="X80" s="21"/>
       <c r="Y80" s="21"/>
       <c r="Z80" s="21"/>
@@ -6589,7 +6852,9 @@
       <c r="V81" s="21">
         <v>0</v>
       </c>
-      <c r="W81" s="21"/>
+      <c r="W81" s="21">
+        <v>0</v>
+      </c>
       <c r="X81" s="21"/>
       <c r="Y81" s="21"/>
       <c r="Z81" s="21"/>
@@ -6650,7 +6915,9 @@
       <c r="V82" s="21">
         <v>4180</v>
       </c>
-      <c r="W82" s="21"/>
+      <c r="W82" s="21">
+        <v>4394</v>
+      </c>
       <c r="X82" s="21"/>
       <c r="Y82" s="21"/>
       <c r="Z82" s="21"/>
@@ -6711,7 +6978,9 @@
       <c r="V83" s="21">
         <v>599</v>
       </c>
-      <c r="W83" s="21"/>
+      <c r="W83" s="21">
+        <v>576</v>
+      </c>
       <c r="X83" s="21"/>
       <c r="Y83" s="21"/>
       <c r="Z83" s="21"/>
@@ -6735,35 +7004,35 @@
         <v>57</v>
       </c>
       <c r="C84" s="21">
-        <f t="shared" ref="C84:J84" si="64">SUM(C80:C83)</f>
+        <f t="shared" ref="C84:J84" si="70">SUM(C80:C83)</f>
         <v>0</v>
       </c>
       <c r="D84" s="21">
-        <f t="shared" si="64"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="E84" s="21">
-        <f t="shared" si="64"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="F84" s="21">
-        <f t="shared" si="64"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="G84" s="21">
-        <f t="shared" si="64"/>
+        <f t="shared" si="70"/>
         <v>4804</v>
       </c>
       <c r="H84" s="21">
-        <f t="shared" si="64"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="I84" s="21">
-        <f t="shared" si="64"/>
+        <f t="shared" si="70"/>
         <v>4999</v>
       </c>
       <c r="J84" s="21">
-        <f t="shared" si="64"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="K84" s="21"/>
@@ -6772,23 +7041,23 @@
       <c r="N84" s="21"/>
       <c r="O84" s="21"/>
       <c r="P84" s="21">
-        <f t="shared" ref="P84:T84" si="65">SUM(P80:P83)</f>
+        <f t="shared" ref="P84:T84" si="71">SUM(P80:P83)</f>
         <v>1618</v>
       </c>
       <c r="Q84" s="21">
-        <f t="shared" si="65"/>
+        <f t="shared" si="71"/>
         <v>6136</v>
       </c>
       <c r="R84" s="21">
-        <f t="shared" si="65"/>
+        <f t="shared" si="71"/>
         <v>5530</v>
       </c>
       <c r="S84" s="21">
-        <f t="shared" si="65"/>
+        <f t="shared" si="71"/>
         <v>5158</v>
       </c>
       <c r="T84" s="21">
-        <f t="shared" si="65"/>
+        <f t="shared" si="71"/>
         <v>4813</v>
       </c>
       <c r="U84" s="21">
@@ -6799,7 +7068,10 @@
         <f>SUM(V80:V83)</f>
         <v>4851</v>
       </c>
-      <c r="W84" s="21"/>
+      <c r="W84" s="21">
+        <f>SUM(W80:W83)</f>
+        <v>5071</v>
+      </c>
       <c r="X84" s="21"/>
       <c r="Y84" s="21"/>
       <c r="Z84" s="21"/>
@@ -6860,7 +7132,9 @@
       <c r="V85" s="21">
         <v>7</v>
       </c>
-      <c r="W85" s="21"/>
+      <c r="W85" s="21">
+        <v>2</v>
+      </c>
       <c r="X85" s="21"/>
       <c r="Y85" s="21"/>
       <c r="Z85" s="21"/>
@@ -6921,7 +7195,9 @@
       <c r="V86" s="21">
         <v>1542</v>
       </c>
-      <c r="W86" s="21"/>
+      <c r="W86" s="21">
+        <v>1539</v>
+      </c>
       <c r="X86" s="21"/>
       <c r="Y86" s="21"/>
       <c r="Z86" s="21"/>
@@ -6982,7 +7258,9 @@
       <c r="V87" s="21">
         <v>8590</v>
       </c>
-      <c r="W87" s="21"/>
+      <c r="W87" s="21">
+        <v>8587</v>
+      </c>
       <c r="X87" s="21"/>
       <c r="Y87" s="21"/>
       <c r="Z87" s="21"/>
@@ -7043,7 +7321,9 @@
       <c r="V88" s="21">
         <v>48</v>
       </c>
-      <c r="W88" s="21"/>
+      <c r="W88" s="21">
+        <v>43</v>
+      </c>
       <c r="X88" s="21"/>
       <c r="Y88" s="21"/>
       <c r="Z88" s="21"/>
@@ -7067,35 +7347,35 @@
         <v>59</v>
       </c>
       <c r="C89" s="21">
-        <f t="shared" ref="C89:J89" si="66">SUM(C85:C88)</f>
+        <f t="shared" ref="C89:J89" si="72">SUM(C85:C88)</f>
         <v>0</v>
       </c>
       <c r="D89" s="21">
-        <f t="shared" si="66"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="E89" s="21">
-        <f t="shared" si="66"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="F89" s="21">
-        <f t="shared" si="66"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="G89" s="21">
-        <f t="shared" si="66"/>
+        <f t="shared" si="72"/>
         <v>11612</v>
       </c>
       <c r="H89" s="21">
-        <f t="shared" si="66"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="I89" s="21">
-        <f t="shared" si="66"/>
+        <f t="shared" si="72"/>
         <v>12952</v>
       </c>
       <c r="J89" s="21">
-        <f t="shared" si="66"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="K89" s="21"/>
@@ -7104,23 +7384,23 @@
       <c r="N89" s="21"/>
       <c r="O89" s="21"/>
       <c r="P89" s="21">
-        <f t="shared" ref="P89:T89" si="67">SUM(P85:P88)</f>
+        <f t="shared" ref="P89:T89" si="73">SUM(P85:P88)</f>
         <v>5382</v>
       </c>
       <c r="Q89" s="21">
-        <f t="shared" si="67"/>
+        <f t="shared" si="73"/>
         <v>7306</v>
       </c>
       <c r="R89" s="21">
-        <f t="shared" si="67"/>
+        <f t="shared" si="73"/>
         <v>6337</v>
       </c>
       <c r="S89" s="21">
-        <f t="shared" si="67"/>
+        <f t="shared" si="73"/>
         <v>8030</v>
       </c>
       <c r="T89" s="21">
-        <f t="shared" si="67"/>
+        <f t="shared" si="73"/>
         <v>8137</v>
       </c>
       <c r="U89" s="21">
@@ -7131,7 +7411,10 @@
         <f>SUM(V85:V88)</f>
         <v>10187</v>
       </c>
-      <c r="W89" s="21"/>
+      <c r="W89" s="21">
+        <f>SUM(W85:W88)</f>
+        <v>10171</v>
+      </c>
       <c r="X89" s="21"/>
       <c r="Y89" s="21"/>
       <c r="Z89" s="21"/>
@@ -7155,35 +7438,35 @@
         <v>60</v>
       </c>
       <c r="C90" s="28">
-        <f t="shared" ref="C90:J90" si="68">C79+C84+C89</f>
+        <f t="shared" ref="C90:J90" si="74">C79+C84+C89</f>
         <v>0</v>
       </c>
       <c r="D90" s="28">
-        <f t="shared" si="68"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="E90" s="28">
-        <f t="shared" si="68"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="F90" s="28">
-        <f t="shared" si="68"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="G90" s="28">
-        <f t="shared" si="68"/>
+        <f t="shared" si="74"/>
         <v>33970</v>
       </c>
       <c r="H90" s="28">
-        <f t="shared" si="68"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="I90" s="28">
-        <f t="shared" si="68"/>
+        <f t="shared" si="74"/>
         <v>36091</v>
       </c>
       <c r="J90" s="28">
-        <f t="shared" si="68"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="K90" s="28"/>
@@ -7192,34 +7475,37 @@
       <c r="N90" s="28"/>
       <c r="O90" s="28"/>
       <c r="P90" s="28">
-        <f t="shared" ref="P90:V90" si="69">P79+P84+P89</f>
+        <f t="shared" ref="P90:W90" si="75">P79+P84+P89</f>
         <v>21683</v>
       </c>
       <c r="Q90" s="28">
-        <f t="shared" si="69"/>
+        <f t="shared" si="75"/>
         <v>28391</v>
       </c>
       <c r="R90" s="28">
-        <f t="shared" si="69"/>
+        <f t="shared" si="75"/>
         <v>26417</v>
       </c>
       <c r="S90" s="28">
-        <f t="shared" si="69"/>
+        <f t="shared" si="75"/>
         <v>28947</v>
       </c>
       <c r="T90" s="28">
-        <f t="shared" si="69"/>
+        <f t="shared" si="75"/>
         <v>29983</v>
       </c>
       <c r="U90" s="28">
-        <f t="shared" si="69"/>
+        <f t="shared" si="75"/>
         <v>32736</v>
       </c>
       <c r="V90" s="28">
-        <f t="shared" si="69"/>
+        <f t="shared" si="75"/>
         <v>34714</v>
       </c>
-      <c r="W90" s="21"/>
+      <c r="W90" s="28">
+        <f t="shared" si="75"/>
+        <v>35637</v>
+      </c>
       <c r="X90" s="21"/>
       <c r="Y90" s="21"/>
       <c r="Z90" s="21"/>
@@ -7338,34 +7624,36 @@
       <c r="N93" s="21"/>
       <c r="O93" s="21"/>
       <c r="P93" s="21">
-        <f t="shared" ref="P93:V93" si="70">P40</f>
+        <f t="shared" ref="P93:W93" si="76">P40</f>
         <v>4428</v>
       </c>
       <c r="Q93" s="21">
-        <f t="shared" si="70"/>
+        <f t="shared" si="76"/>
         <v>4682</v>
       </c>
       <c r="R93" s="21">
-        <f t="shared" si="70"/>
+        <f t="shared" si="76"/>
         <v>1400</v>
       </c>
       <c r="S93" s="21">
-        <f t="shared" si="70"/>
+        <f t="shared" si="76"/>
         <v>4198</v>
       </c>
       <c r="T93" s="21">
-        <f t="shared" si="70"/>
+        <f t="shared" si="76"/>
         <v>5357</v>
       </c>
       <c r="U93" s="21">
-        <f t="shared" si="70"/>
+        <f t="shared" si="76"/>
         <v>6869</v>
       </c>
       <c r="V93" s="21">
-        <f t="shared" si="70"/>
+        <f t="shared" si="76"/>
         <v>7577</v>
       </c>
-      <c r="W93" s="21"/>
+      <c r="W93" s="21">
+        <v>8020</v>
+      </c>
       <c r="X93" s="21"/>
       <c r="Y93" s="21"/>
       <c r="Z93" s="21"/>
@@ -7424,7 +7712,9 @@
       <c r="V94" s="21">
         <v>3174</v>
       </c>
-      <c r="W94" s="21"/>
+      <c r="W94" s="21">
+        <v>3270</v>
+      </c>
       <c r="X94" s="21"/>
       <c r="Y94" s="21"/>
       <c r="Z94" s="21"/>
@@ -7483,7 +7773,9 @@
       <c r="V95" s="21">
         <v>223</v>
       </c>
-      <c r="W95" s="21"/>
+      <c r="W95" s="21">
+        <v>215</v>
+      </c>
       <c r="X95" s="21"/>
       <c r="Y95" s="21"/>
       <c r="Z95" s="21"/>
@@ -7544,7 +7836,9 @@
       <c r="V96" s="21">
         <v>51</v>
       </c>
-      <c r="W96" s="21"/>
+      <c r="W96" s="21">
+        <v>114</v>
+      </c>
       <c r="X96" s="21"/>
       <c r="Y96" s="21"/>
       <c r="Z96" s="21"/>
@@ -7603,7 +7897,9 @@
       <c r="V97" s="21">
         <v>-1539</v>
       </c>
-      <c r="W97" s="21"/>
+      <c r="W97" s="21">
+        <v>-1585</v>
+      </c>
       <c r="X97" s="21"/>
       <c r="Y97" s="21"/>
       <c r="Z97" s="21"/>
@@ -7707,7 +8003,9 @@
       <c r="V99" s="21">
         <v>-427</v>
       </c>
-      <c r="W99" s="21"/>
+      <c r="W99" s="21">
+        <v>9</v>
+      </c>
       <c r="X99" s="21"/>
       <c r="Y99" s="21"/>
       <c r="Z99" s="21"/>
@@ -7766,7 +8064,9 @@
       <c r="V100" s="21">
         <v>-164</v>
       </c>
-      <c r="W100" s="21"/>
+      <c r="W100" s="21">
+        <v>-149</v>
+      </c>
       <c r="X100" s="21"/>
       <c r="Y100" s="21"/>
       <c r="Z100" s="21"/>
@@ -7825,7 +8125,9 @@
       <c r="V101" s="21">
         <v>392</v>
       </c>
-      <c r="W101" s="21"/>
+      <c r="W101" s="21">
+        <v>-663</v>
+      </c>
       <c r="X101" s="21"/>
       <c r="Y101" s="21"/>
       <c r="Z101" s="21"/>
@@ -7864,19 +8166,19 @@
       <c r="N102" s="21"/>
       <c r="O102" s="21"/>
       <c r="P102" s="21">
-        <f t="shared" ref="P102:S102" si="71">SUM(P99:P101)</f>
+        <f t="shared" ref="P102:S102" si="77">SUM(P99:P101)</f>
         <v>-349</v>
       </c>
       <c r="Q102" s="21">
-        <f t="shared" si="71"/>
+        <f t="shared" si="77"/>
         <v>205</v>
       </c>
       <c r="R102" s="21">
-        <f t="shared" si="71"/>
+        <f t="shared" si="77"/>
         <v>-847</v>
       </c>
       <c r="S102" s="21">
-        <f t="shared" si="71"/>
+        <f t="shared" si="77"/>
         <v>223</v>
       </c>
       <c r="T102" s="21">
@@ -7891,7 +8193,10 @@
         <f>SUM(V99:V101)</f>
         <v>-199</v>
       </c>
-      <c r="W102" s="21"/>
+      <c r="W102" s="21">
+        <f>SUM(W99:W101)</f>
+        <v>-803</v>
+      </c>
       <c r="X102" s="21"/>
       <c r="Y102" s="21"/>
       <c r="Z102" s="21"/>
@@ -7930,23 +8235,23 @@
       <c r="N103" s="28"/>
       <c r="O103" s="28"/>
       <c r="P103" s="28">
-        <f t="shared" ref="P103:T103" si="72">P93+SUM(P94:P97)+P102</f>
+        <f t="shared" ref="P103:T103" si="78">P93+SUM(P94:P97)+P102</f>
         <v>4028</v>
       </c>
       <c r="Q103" s="28">
-        <f t="shared" si="72"/>
+        <f t="shared" si="78"/>
         <v>6901</v>
       </c>
       <c r="R103" s="28">
-        <f t="shared" si="72"/>
+        <f t="shared" si="78"/>
         <v>3016</v>
       </c>
       <c r="S103" s="28">
-        <f t="shared" si="72"/>
+        <f t="shared" si="78"/>
         <v>6754</v>
       </c>
       <c r="T103" s="28">
-        <f t="shared" si="72"/>
+        <f t="shared" si="78"/>
         <v>6673</v>
       </c>
       <c r="U103" s="28">
@@ -7957,7 +8262,10 @@
         <f>V93+SUM(V94:V97)+V102</f>
         <v>9287</v>
       </c>
-      <c r="W103" s="21"/>
+      <c r="W103" s="28">
+        <f>W93+SUM(W94:W97)+W102</f>
+        <v>9231</v>
+      </c>
       <c r="X103" s="21"/>
       <c r="Y103" s="21"/>
       <c r="Z103" s="21"/>
@@ -8016,7 +8324,9 @@
       <c r="V104" s="21">
         <v>-465</v>
       </c>
-      <c r="W104" s="21"/>
+      <c r="W104" s="21">
+        <v>-519</v>
+      </c>
       <c r="X104" s="21"/>
       <c r="Y104" s="21"/>
       <c r="Z104" s="21"/>
@@ -8078,7 +8388,9 @@
       <c r="V105" s="21">
         <v>-2207</v>
       </c>
-      <c r="W105" s="21"/>
+      <c r="W105" s="21">
+        <v>-2193</v>
+      </c>
       <c r="X105" s="21"/>
       <c r="Y105" s="21"/>
       <c r="Z105" s="21"/>
@@ -8138,7 +8450,10 @@
         <f>51-14</f>
         <v>37</v>
       </c>
-      <c r="W106" s="21"/>
+      <c r="W106" s="21">
+        <f>-16+55</f>
+        <v>39</v>
+      </c>
       <c r="X106" s="21"/>
       <c r="Y106" s="21"/>
       <c r="Z106" s="21"/>
@@ -8197,7 +8512,9 @@
       <c r="V107" s="21">
         <v>51</v>
       </c>
-      <c r="W107" s="21"/>
+      <c r="W107" s="21">
+        <v>3</v>
+      </c>
       <c r="X107" s="21"/>
       <c r="Y107" s="21"/>
       <c r="Z107" s="21"/>
@@ -8256,7 +8573,9 @@
       <c r="V108" s="21">
         <v>-705</v>
       </c>
-      <c r="W108" s="21"/>
+      <c r="W108" s="21">
+        <v>-545</v>
+      </c>
       <c r="X108" s="21"/>
       <c r="Y108" s="21"/>
       <c r="Z108" s="21"/>
@@ -8295,23 +8614,23 @@
       <c r="N109" s="28"/>
       <c r="O109" s="28"/>
       <c r="P109" s="28">
-        <f t="shared" ref="P109:T109" si="73">SUM(P104:P108)</f>
+        <f t="shared" ref="P109:T109" si="79">SUM(P104:P108)</f>
         <v>-1875</v>
       </c>
       <c r="Q109" s="28">
-        <f t="shared" si="73"/>
+        <f t="shared" si="79"/>
         <v>-2376</v>
       </c>
       <c r="R109" s="28">
-        <f t="shared" si="73"/>
+        <f t="shared" si="79"/>
         <v>2514</v>
       </c>
       <c r="S109" s="28">
-        <f t="shared" si="73"/>
+        <f t="shared" si="79"/>
         <v>-3253</v>
       </c>
       <c r="T109" s="28">
-        <f t="shared" si="73"/>
+        <f t="shared" si="79"/>
         <v>-3503</v>
       </c>
       <c r="U109" s="28">
@@ -8322,7 +8641,10 @@
         <f>SUM(V104:V108)</f>
         <v>-3289</v>
       </c>
-      <c r="W109" s="21"/>
+      <c r="W109" s="28">
+        <f>SUM(W104:W108)</f>
+        <v>-3215</v>
+      </c>
       <c r="X109" s="21"/>
       <c r="Y109" s="21"/>
       <c r="Z109" s="21"/>
@@ -8381,7 +8703,9 @@
       <c r="V110" s="21">
         <v>0</v>
       </c>
-      <c r="W110" s="21"/>
+      <c r="W110" s="21">
+        <v>0</v>
+      </c>
       <c r="X110" s="21"/>
       <c r="Y110" s="21"/>
       <c r="Z110" s="21"/>
@@ -8440,7 +8764,9 @@
       <c r="V111" s="21">
         <v>0</v>
       </c>
-      <c r="W111" s="21"/>
+      <c r="W111" s="21">
+        <v>0</v>
+      </c>
       <c r="X111" s="21"/>
       <c r="Y111" s="21"/>
       <c r="Z111" s="21"/>
@@ -8499,7 +8825,9 @@
       <c r="V112" s="21">
         <v>-8</v>
       </c>
-      <c r="W112" s="21"/>
+      <c r="W112" s="21">
+        <v>-5</v>
+      </c>
       <c r="X112" s="21"/>
       <c r="Y112" s="21"/>
       <c r="Z112" s="21"/>
@@ -8558,7 +8886,9 @@
       <c r="V113" s="21">
         <v>-1802</v>
       </c>
-      <c r="W113" s="21"/>
+      <c r="W113" s="21">
+        <v>-1834</v>
+      </c>
       <c r="X113" s="21"/>
       <c r="Y113" s="21"/>
       <c r="Z113" s="21"/>
@@ -8617,7 +8947,9 @@
       <c r="V114" s="21">
         <v>-4797</v>
       </c>
-      <c r="W114" s="21"/>
+      <c r="W114" s="21">
+        <v>-5235</v>
+      </c>
       <c r="X114" s="21"/>
       <c r="Y114" s="21"/>
       <c r="Z114" s="21"/>
@@ -8656,23 +8988,23 @@
       <c r="N115" s="28"/>
       <c r="O115" s="28"/>
       <c r="P115" s="28">
-        <f t="shared" ref="P115:T115" si="74">SUM(P110:P114)</f>
+        <f t="shared" ref="P115:T115" si="80">SUM(P110:P114)</f>
         <v>-2260</v>
       </c>
       <c r="Q115" s="28">
-        <f t="shared" si="74"/>
+        <f t="shared" si="80"/>
         <v>-4629</v>
       </c>
       <c r="R115" s="28">
-        <f t="shared" si="74"/>
+        <f t="shared" si="80"/>
         <v>-2786</v>
       </c>
       <c r="S115" s="28">
-        <f t="shared" si="74"/>
+        <f t="shared" si="80"/>
         <v>-3909</v>
       </c>
       <c r="T115" s="28">
-        <f t="shared" si="74"/>
+        <f t="shared" si="80"/>
         <v>-4614</v>
       </c>
       <c r="U115" s="28">
@@ -8683,7 +9015,10 @@
         <f>SUM(V110:V114)</f>
         <v>-6607</v>
       </c>
-      <c r="W115" s="21"/>
+      <c r="W115" s="28">
+        <f>SUM(W110:W114)</f>
+        <v>-7074</v>
+      </c>
       <c r="X115" s="21"/>
       <c r="Y115" s="21"/>
       <c r="Z115" s="21"/>
@@ -8742,7 +9077,9 @@
       <c r="V116" s="21">
         <v>-18</v>
       </c>
-      <c r="W116" s="21"/>
+      <c r="W116" s="21">
+        <v>-48</v>
+      </c>
       <c r="X116" s="21"/>
       <c r="Y116" s="21"/>
       <c r="Z116" s="21"/>
@@ -8824,23 +9161,23 @@
       <c r="N118" s="28"/>
       <c r="O118" s="28"/>
       <c r="P118" s="28">
-        <f t="shared" ref="P118:T118" si="75">P103+P109+P115+P116</f>
+        <f t="shared" ref="P118:T118" si="81">P103+P109+P115+P116</f>
         <v>-66</v>
       </c>
       <c r="Q118" s="28">
-        <f t="shared" si="75"/>
+        <f t="shared" si="81"/>
         <v>-84</v>
       </c>
       <c r="R118" s="28">
-        <f t="shared" si="75"/>
+        <f t="shared" si="81"/>
         <v>2617</v>
       </c>
       <c r="S118" s="28">
-        <f t="shared" si="75"/>
+        <f t="shared" si="81"/>
         <v>-377</v>
       </c>
       <c r="T118" s="28">
-        <f t="shared" si="75"/>
+        <f t="shared" si="81"/>
         <v>-1461</v>
       </c>
       <c r="U118" s="28">
@@ -8851,7 +9188,10 @@
         <f>V103+V109+V115+V116</f>
         <v>-627</v>
       </c>
-      <c r="W118" s="21"/>
+      <c r="W118" s="28">
+        <f>W103+W109+W115+W116</f>
+        <v>-1106</v>
+      </c>
       <c r="X118" s="21"/>
       <c r="Y118" s="21"/>
       <c r="Z118" s="21"/>
@@ -8911,7 +9251,9 @@
         <f>+U120</f>
         <v>7007</v>
       </c>
-      <c r="W119" s="21"/>
+      <c r="W119" s="21">
+        <v>6382</v>
+      </c>
       <c r="X119" s="21"/>
       <c r="Y119" s="21"/>
       <c r="Z119" s="21"/>
@@ -8973,10 +9315,12 @@
         <v>7007</v>
       </c>
       <c r="V120" s="21">
-        <f>+V118+V119</f>
-        <v>6380</v>
-      </c>
-      <c r="W120" s="21"/>
+        <v>6382</v>
+      </c>
+      <c r="W120" s="21">
+        <f>+W118+W119</f>
+        <v>5276</v>
+      </c>
       <c r="X120" s="21"/>
       <c r="Y120" s="21"/>
       <c r="Z120" s="21"/>
@@ -9620,6 +9964,9 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
+      <c r="K2" s="82" t="s">
+        <v>203</v>
+      </c>
       <c r="M2" s="6" t="s">
         <v>102</v>
       </c>
@@ -9664,6 +10011,10 @@
         <f>Model!V44/Model!V77</f>
         <v>0.29812970115877213</v>
       </c>
+      <c r="K4" s="29">
+        <f>Model!W44/Model!W77</f>
+        <v>0.30492767835253737</v>
+      </c>
       <c r="M4" s="31">
         <f>AVERAGE(G4:I4,D4:E4)</f>
         <v>0.24330939583428152</v>
@@ -9701,6 +10052,10 @@
         <f>Model!V37/Model!V75</f>
         <v>0.21764180566358424</v>
       </c>
+      <c r="K5" s="29">
+        <f>Model!W37/Model!W75</f>
+        <v>0.22439530837869689</v>
+      </c>
       <c r="M5" s="31">
         <f t="shared" ref="M5:M12" si="1">AVERAGE(G5:I5,D5:E5)</f>
         <v>0.18179771204849587</v>
@@ -9738,6 +10093,10 @@
         <f>(Model!V37*(1-Model!V61))/(Model!V79+Model!V82+Model!V83+Model!V85+Model!V86-Model!V72-Model!V71)</f>
         <v>0.40407778171959441</v>
       </c>
+      <c r="K6" s="29">
+        <f>(Model!W37*(1-Model!W61))/(Model!W79+Model!W82+Model!W83+Model!W85+Model!W86-Model!W72-Model!W71)</f>
+        <v>0.38893379352846724</v>
+      </c>
       <c r="M6" s="31">
         <f t="shared" si="1"/>
         <v>0.3229640520512535</v>
@@ -9775,6 +10134,10 @@
         <f>Model!V37/(Model!V68+Model!V69+Model!V70+Model!V73-Model!V87)</f>
         <v>0.51672252239928873</v>
       </c>
+      <c r="K7" s="29">
+        <f>Model!W37/(Model!W68+Model!W69+Model!W70+Model!W73-Model!W87)</f>
+        <v>0.49698589273506927</v>
+      </c>
       <c r="M7" s="31">
         <f t="shared" si="1"/>
         <v>0.40156832033852741</v>
@@ -9812,6 +10175,10 @@
         <f>1-(-Model!V114/Model!V44)</f>
         <v>0.18223661779747702</v>
       </c>
+      <c r="K9" s="29">
+        <f>1-(-Model!W114/Model!W44)</f>
+        <v>0.15822479498311626</v>
+      </c>
       <c r="M9" s="31">
         <f t="shared" si="1"/>
         <v>0.29824215919913161</v>
@@ -9849,6 +10216,10 @@
         <f>J9*J4</f>
         <v>5.4330148404147197E-2</v>
       </c>
+      <c r="K10" s="29">
+        <f>K9*K4</f>
+        <v>4.8247119392007841E-2</v>
+      </c>
       <c r="M10" s="31">
         <f t="shared" si="1"/>
         <v>7.2380326383010479E-2</v>
@@ -9886,6 +10257,10 @@
         <f>(-Model!V102-Model!V109)/(Model!V37*(1-Model!V61))</f>
         <v>0.59522834475600461</v>
       </c>
+      <c r="K11" s="29">
+        <f>(-Model!W102-Model!W109)/(Model!W37*(1-Model!W61))</f>
+        <v>0.64786197863272532</v>
+      </c>
       <c r="M11" s="31">
         <f t="shared" si="1"/>
         <v>0.69220579605523258</v>
@@ -9923,6 +10298,10 @@
         <f>J11*J6</f>
         <v>0.24051854916563231</v>
       </c>
+      <c r="K12" s="29">
+        <f>K11*K6</f>
+        <v>0.25197541703248466</v>
+      </c>
       <c r="M12" s="31">
         <f t="shared" si="1"/>
         <v>0.21680303648478247</v>
@@ -9994,6 +10373,10 @@
         <f>Model!V70/Model!V29*360</f>
         <v>10.138745081797474</v>
       </c>
+      <c r="K20" s="34">
+        <f>Model!W70/Model!W29*360</f>
+        <v>10.529801324503312</v>
+      </c>
       <c r="M20" s="34">
         <f>AVERAGE(D20:I20)</f>
         <v>10.7620912646356</v>
@@ -10031,6 +10414,10 @@
         <f>Model!V87/Model!V29*360</f>
         <v>80.047628908676742</v>
       </c>
+      <c r="K21" s="34">
+        <f>Model!W87/Model!W29*360</f>
+        <v>77.546658639373874</v>
+      </c>
       <c r="M21" s="34">
         <f t="shared" ref="M21" si="5">AVERAGE(D21:I21)</f>
         <v>76.286243662656872</v>
@@ -10068,6 +10455,10 @@
         <f>Model!V69/Model!V75</f>
         <v>9.5670210007778062E-2</v>
       </c>
+      <c r="K22" s="29">
+        <f>Model!W69/Model!W75</f>
+        <v>9.1166732139850715E-2</v>
+      </c>
       <c r="M22" s="29">
         <f>AVERAGE(D22:I22)</f>
         <v>9.9192630389692948E-2</v>
@@ -10105,6 +10496,10 @@
         <f>Model!V30/Model!V69</f>
         <v>4.9045468232460099</v>
       </c>
+      <c r="K23" s="34">
+        <f>Model!W30/Model!W69</f>
+        <v>5.1221914435210838</v>
+      </c>
       <c r="M23" s="34">
         <f>AVERAGE(D23:I23)</f>
         <v>4.4962663945444374</v>
@@ -10142,6 +10537,10 @@
         <f>360/J23</f>
         <v>73.401277013752463</v>
       </c>
+      <c r="K24" s="34">
+        <f>360/K23</f>
+        <v>70.282417978608336</v>
+      </c>
       <c r="M24" s="34">
         <f>AVERAGE(D24:I24)</f>
         <v>81.463770183431748</v>
@@ -10179,6 +10578,10 @@
         <f>J24+J20-J21</f>
         <v>3.4923931868732012</v>
       </c>
+      <c r="K25" s="34">
+        <f>K24+K20-K21</f>
+        <v>3.265560663737773</v>
+      </c>
       <c r="M25" s="34">
         <f>AVERAGE(D25:I25)</f>
         <v>15.939617785410475</v>
@@ -10215,8 +10618,10 @@
         <v>42.73</v>
       </c>
       <c r="J29" s="3">
-        <f>Main!J3</f>
-        <v>54.86</v>
+        <v>59</v>
+      </c>
+      <c r="K29" s="3">
+        <v>52.8</v>
       </c>
       <c r="M29" s="34"/>
     </row>
@@ -10252,6 +10657,10 @@
         <f>Model!V47</f>
         <v>3144.4529830000001</v>
       </c>
+      <c r="K30" s="3">
+        <f>Model!W47</f>
+        <v>3116.0914859999998</v>
+      </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
@@ -10283,7 +10692,11 @@
       </c>
       <c r="J31" s="21">
         <f>J29*J30</f>
-        <v>172504.69064738002</v>
+        <v>185522.725997</v>
+      </c>
+      <c r="K31" s="21">
+        <f>K29*K30</f>
+        <v>164529.63046079999</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
@@ -10315,8 +10728,12 @@
         <v>-6253</v>
       </c>
       <c r="J32" s="21">
-        <f>Main!J7-Main!J6</f>
-        <v>-11268</v>
+        <f>Model!V81+Model!V82+Model!V85+Model!V86-Model!V72-Model!V71-Model!V66</f>
+        <v>-6223</v>
+      </c>
+      <c r="K32" s="21">
+        <f>Model!W81+Model!W82+Model!W85+Model!W86-Model!W72-Model!W71-Model!W66</f>
+        <v>-5496</v>
       </c>
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.2">
@@ -10348,8 +10765,12 @@
         <v>126758.50582422997</v>
       </c>
       <c r="J33" s="21">
-        <f>J31+J32</f>
-        <v>161236.69064738002</v>
+        <f t="shared" ref="J33:K33" si="10">J31+J32</f>
+        <v>179299.725997</v>
+      </c>
+      <c r="K33" s="21">
+        <f t="shared" si="10"/>
+        <v>159033.63046079999</v>
       </c>
     </row>
     <row r="34" spans="2:13" x14ac:dyDescent="0.2">
@@ -10387,7 +10808,11 @@
       </c>
       <c r="J35" s="34">
         <f>J31/Model!V44</f>
-        <v>29.407550400167068</v>
+        <v>31.626785884248211</v>
+      </c>
+      <c r="K35" s="34">
+        <f>K31/Model!W44</f>
+        <v>26.455962447467439</v>
       </c>
       <c r="M35" s="34">
         <f>AVERAGE(G35:I35,D35:E35)</f>
@@ -10421,10 +10846,14 @@
       </c>
       <c r="J36" s="35">
         <f>J35/((Model!V44/Model!U44-1)*100)</f>
-        <v>3.255403727425902</v>
+        <v>3.5010721822480533</v>
+      </c>
+      <c r="K36" s="35">
+        <f>K35/((Model!W44/Model!V44-1)*100)</f>
+        <v>4.3963364225734907</v>
       </c>
       <c r="M36" s="34">
-        <f t="shared" ref="M36:M37" si="10">AVERAGE(G36:I36,D36:E36)</f>
+        <f t="shared" ref="M36:M37" si="11">AVERAGE(G36:I36,D36:E36)</f>
         <v>1.6992391622853413</v>
       </c>
     </row>
@@ -10459,8 +10888,11 @@
       <c r="J37" s="6" t="s">
         <v>130</v>
       </c>
+      <c r="K37" s="6" t="s">
+        <v>130</v>
+      </c>
       <c r="M37" s="34">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>6.3153374150430803</v>
       </c>
     </row>
@@ -10500,10 +10932,14 @@
       </c>
       <c r="J39" s="34">
         <f>J33/Model!V29</f>
-        <v>4.1736563120568446</v>
+        <v>4.6412229756937258</v>
+      </c>
+      <c r="K39" s="34">
+        <f>K33/Model!W29</f>
+        <v>3.9894047376279347</v>
       </c>
       <c r="M39" s="34">
-        <f t="shared" ref="M39:M41" si="11">AVERAGE(G39:I39,D39:E39)</f>
+        <f t="shared" ref="M39:M41" si="12">AVERAGE(G39:I39,D39:E39)</f>
         <v>3.2484739151977018</v>
       </c>
     </row>
@@ -10537,10 +10973,14 @@
       </c>
       <c r="J40" s="34">
         <f>J33/Model!V34</f>
-        <v>15.028119176752728</v>
+        <v>16.711690371609656</v>
+      </c>
+      <c r="K40" s="34">
+        <f>K33/Model!W34</f>
+        <v>14.114993384290404</v>
       </c>
       <c r="M40" s="34">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>12.810684527546437</v>
       </c>
     </row>
@@ -10574,10 +11014,14 @@
       </c>
       <c r="J41" s="34">
         <f>J33/Model!V37</f>
-        <v>21.34171947682065</v>
+        <v>23.732591131303774</v>
+      </c>
+      <c r="K41" s="34">
+        <f>K33/Model!W37</f>
+        <v>19.886661305589595</v>
       </c>
       <c r="M41" s="34">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>19.181670394772546</v>
       </c>
     </row>
@@ -10650,7 +11094,7 @@
       </c>
       <c r="J3" s="38">
         <f>Main!J3</f>
-        <v>54.86</v>
+        <v>52.82</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.2">
@@ -10665,7 +11109,7 @@
       </c>
       <c r="J4" s="40">
         <f ca="1">V60</f>
-        <v>69.266675579291473</v>
+        <v>69.165129822077631</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.2">
@@ -10680,7 +11124,7 @@
       </c>
       <c r="J5" s="41">
         <f ca="1">J4/J3-1</f>
-        <v>0.26260801274683687</v>
+        <v>0.30944963691930383</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.2">
@@ -12369,7 +12813,7 @@
       <c r="Q56" s="3"/>
       <c r="V56" s="3">
         <f>Main!J6</f>
-        <v>11269</v>
+        <v>10960</v>
       </c>
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.2">
@@ -12397,7 +12841,7 @@
       <c r="U57" s="68"/>
       <c r="V57" s="68">
         <f>Main!J7</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.2">
@@ -12410,7 +12854,7 @@
       <c r="Q58" s="3"/>
       <c r="V58" s="3">
         <f ca="1">V55+V56-V57</f>
-        <v>215834.87216666079</v>
+        <v>215524.87216666079</v>
       </c>
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.2">
@@ -12438,7 +12882,7 @@
       <c r="U59" s="68"/>
       <c r="V59" s="68">
         <f>Main!J4</f>
-        <v>3115.9987160000001</v>
+        <v>3116.0914859999998</v>
       </c>
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.2">
@@ -12447,7 +12891,7 @@
       </c>
       <c r="V60" s="34">
         <f ca="1">V58/V59</f>
-        <v>69.266675579291473</v>
+        <v>69.165129822077631</v>
       </c>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.2">
@@ -12480,19 +12924,19 @@
     </row>
     <row r="66" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B66" s="70"/>
-      <c r="C66" s="75" t="s">
+      <c r="C66" s="77" t="s">
         <v>163</v>
       </c>
-      <c r="D66" s="75"/>
-      <c r="E66" s="75"/>
-      <c r="F66" s="75"/>
-      <c r="G66" s="75"/>
-      <c r="H66" s="75"/>
-      <c r="I66" s="75"/>
-      <c r="J66" s="76"/>
+      <c r="D66" s="77"/>
+      <c r="E66" s="77"/>
+      <c r="F66" s="77"/>
+      <c r="G66" s="77"/>
+      <c r="H66" s="77"/>
+      <c r="I66" s="77"/>
+      <c r="J66" s="78"/>
     </row>
     <row r="67" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B67" s="77" t="s">
+      <c r="B67" s="79" t="s">
         <v>162</v>
       </c>
       <c r="C67" s="71"/>
@@ -12505,7 +12949,7 @@
       <c r="J67" s="72"/>
     </row>
     <row r="68" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B68" s="77"/>
+      <c r="B68" s="79"/>
       <c r="C68" s="73"/>
       <c r="D68" s="35"/>
       <c r="E68" s="35"/>
@@ -12516,7 +12960,7 @@
       <c r="J68" s="35"/>
     </row>
     <row r="69" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B69" s="77"/>
+      <c r="B69" s="79"/>
       <c r="C69" s="73"/>
       <c r="D69" s="35"/>
       <c r="E69" s="35"/>
@@ -12527,7 +12971,7 @@
       <c r="J69" s="35"/>
     </row>
     <row r="70" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B70" s="77"/>
+      <c r="B70" s="79"/>
       <c r="C70" s="73"/>
       <c r="D70" s="35"/>
       <c r="E70" s="35"/>
@@ -12538,7 +12982,7 @@
       <c r="J70" s="35"/>
     </row>
     <row r="71" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B71" s="77"/>
+      <c r="B71" s="79"/>
       <c r="C71" s="73"/>
       <c r="D71" s="35"/>
       <c r="E71" s="35"/>
@@ -12549,7 +12993,7 @@
       <c r="J71" s="35"/>
     </row>
     <row r="72" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B72" s="77"/>
+      <c r="B72" s="79"/>
       <c r="C72" s="73"/>
       <c r="D72" s="35"/>
       <c r="E72" s="35"/>
@@ -12560,7 +13004,7 @@
       <c r="J72" s="35"/>
     </row>
     <row r="73" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B73" s="77"/>
+      <c r="B73" s="79"/>
       <c r="C73" s="73"/>
       <c r="D73" s="35"/>
       <c r="E73" s="35"/>
@@ -12571,7 +13015,7 @@
       <c r="J73" s="35"/>
     </row>
     <row r="74" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B74" s="78"/>
+      <c r="B74" s="80"/>
       <c r="C74" s="73"/>
       <c r="D74" s="35"/>
       <c r="E74" s="35"/>

--- a/ITX.MC.xlsx
+++ b/ITX.MC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58E19782-CF03-4F9B-9358-218FED79A078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9134760F-4D04-47BF-9CE3-A6638240F452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{D8A593F9-CE2E-4D8C-B815-D7E0264BAFFB}"/>
+    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" xr2:uid="{D8A593F9-CE2E-4D8C-B815-D7E0264BAFFB}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -113,7 +113,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="207">
   <si>
     <t>Inditex</t>
   </si>
@@ -725,6 +725,15 @@
   </si>
   <si>
     <t>FY25</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>John Galliano will desing collections for Zara:</t>
+  </si>
+  <si>
+    <t>https://www.businessoffashion.com/articles/retail/zara-taps-john-galliano-to-design-seasonal-collections/</t>
   </si>
 </sst>
 </file>
@@ -744,13 +753,19 @@
     <numFmt numFmtId="173" formatCode="#,##0;\(#,##0\)"/>
     <numFmt numFmtId="174" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1095,134 +1110,135 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="173" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="173" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="173" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="171" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="173" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="173" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="173" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="5" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="3" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="5" fillId="3" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="170" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="170" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="4" fillId="3" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="5" fillId="3" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="16" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="9" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="9" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="16" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="17" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="10" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="10" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="173" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="174" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -1681,7 +1697,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31B0593E-5163-482C-A654-07C73293509B}">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.5703125" style="2" customWidth="1"/>
@@ -1725,10 +1741,10 @@
       <c r="I4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="J4" s="81">
+      <c r="J4" s="77">
         <v>3116.0914859999998</v>
       </c>
-      <c r="K4" s="82" t="s">
+      <c r="K4" s="78" t="s">
         <v>194</v>
       </c>
     </row>
@@ -1758,7 +1774,7 @@
         <f>5276+5684</f>
         <v>10960</v>
       </c>
-      <c r="K6" s="82" t="s">
+      <c r="K6" s="78" t="s">
         <v>194</v>
       </c>
     </row>
@@ -1785,7 +1801,7 @@
       <c r="J7" s="5">
         <v>2</v>
       </c>
-      <c r="K7" s="82" t="s">
+      <c r="K7" s="78" t="s">
         <v>194</v>
       </c>
     </row>
@@ -1882,9 +1898,24 @@
       <c r="F13" s="18"/>
       <c r="G13" s="19"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B15" s="76" t="s">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B17" s="46" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B18" s="76" t="s">
         <v>202</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B19" s="84" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B20" s="2" t="s">
+        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -2512,7 +2543,7 @@
         <v>29149.919999999998</v>
       </c>
       <c r="X12" s="21">
-        <f t="shared" ref="W12:AA12" si="4">X13*X10</f>
+        <f t="shared" ref="X12:AA12" si="4">X13*X10</f>
         <v>29689.193519999997</v>
       </c>
       <c r="Y12" s="21">
@@ -2580,7 +2611,7 @@
         <v>5.3388131868131863</v>
       </c>
       <c r="X13" s="21">
-        <f t="shared" ref="W13:AA13" si="6">W13*1.05</f>
+        <f t="shared" ref="X13:AA13" si="6">W13*1.05</f>
         <v>5.6057538461538456</v>
       </c>
       <c r="Y13" s="21">
@@ -2697,7 +2728,7 @@
         <v>10714.08</v>
       </c>
       <c r="X15" s="21">
-        <f t="shared" ref="W15:AA15" si="8">X17*X20</f>
+        <f t="shared" ref="X15:AA15" si="8">X17*X20</f>
         <v>11254.069632000001</v>
       </c>
       <c r="Y15" s="21">
@@ -3487,7 +3518,7 @@
         <f>11361-SUM(K30:L30)</f>
         <v>3707</v>
       </c>
-      <c r="N30" s="83">
+      <c r="N30" s="79">
         <f>+W30-SUM(K30:M30)</f>
         <v>5281</v>
       </c>
@@ -3656,7 +3687,7 @@
         <f>8479-SUM(K32:L32)</f>
         <v>2895</v>
       </c>
-      <c r="N32" s="83">
+      <c r="N32" s="79">
         <f>+W32-SUM(K32:M32)</f>
         <v>3399</v>
       </c>
@@ -3733,7 +3764,7 @@
         <f>-29-SUM(K33:L33)</f>
         <v>-24</v>
       </c>
-      <c r="N33" s="83">
+      <c r="N33" s="79">
         <f>+W33-SUM(K33:M33)</f>
         <v>-48</v>
       </c>
@@ -3898,7 +3929,7 @@
       <c r="M35" s="21">
         <v>0</v>
       </c>
-      <c r="N35" s="83">
+      <c r="N35" s="79">
         <f>+W35-SUM(K35:M35)</f>
         <v>0</v>
       </c>
@@ -3974,7 +4005,7 @@
         <f>2359-SUM(K36:L36)</f>
         <v>817</v>
       </c>
-      <c r="N36" s="83">
+      <c r="N36" s="79">
         <f>+W36-SUM(K36:M36)</f>
         <v>911</v>
       </c>
@@ -4143,7 +4174,7 @@
         <f>-49-SUM(K38:L38)</f>
         <v>-37</v>
       </c>
-      <c r="N38" s="83">
+      <c r="N38" s="79">
         <f>+W38-SUM(K38:M38)</f>
         <v>-31</v>
       </c>
@@ -4220,7 +4251,7 @@
         <f>69-SUM(K39:L39)</f>
         <v>27</v>
       </c>
-      <c r="N39" s="83">
+      <c r="N39" s="79">
         <f>+W39-SUM(K39:M39)</f>
         <v>33</v>
       </c>
@@ -4387,7 +4418,7 @@
         <f>1341-SUM(K41:L41)</f>
         <v>531</v>
       </c>
-      <c r="N41" s="83">
+      <c r="N41" s="79">
         <f>+W41-SUM(K41:M41)</f>
         <v>459</v>
       </c>
@@ -4552,7 +4583,7 @@
       <c r="M43" s="21">
         <v>0</v>
       </c>
-      <c r="N43" s="83">
+      <c r="N43" s="79">
         <f>+W43-SUM(K43:M43)</f>
         <v>0</v>
       </c>
@@ -7624,7 +7655,7 @@
       <c r="N93" s="21"/>
       <c r="O93" s="21"/>
       <c r="P93" s="21">
-        <f t="shared" ref="P93:W93" si="76">P40</f>
+        <f t="shared" ref="P93:V93" si="76">P40</f>
         <v>4428</v>
       </c>
       <c r="Q93" s="21">
@@ -9964,7 +9995,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="K2" s="82" t="s">
+      <c r="K2" s="78" t="s">
         <v>203</v>
       </c>
       <c r="M2" s="6" t="s">
@@ -12924,19 +12955,19 @@
     </row>
     <row r="66" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B66" s="70"/>
-      <c r="C66" s="77" t="s">
+      <c r="C66" s="80" t="s">
         <v>163</v>
       </c>
-      <c r="D66" s="77"/>
-      <c r="E66" s="77"/>
-      <c r="F66" s="77"/>
-      <c r="G66" s="77"/>
-      <c r="H66" s="77"/>
-      <c r="I66" s="77"/>
-      <c r="J66" s="78"/>
+      <c r="D66" s="80"/>
+      <c r="E66" s="80"/>
+      <c r="F66" s="80"/>
+      <c r="G66" s="80"/>
+      <c r="H66" s="80"/>
+      <c r="I66" s="80"/>
+      <c r="J66" s="81"/>
     </row>
     <row r="67" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B67" s="79" t="s">
+      <c r="B67" s="82" t="s">
         <v>162</v>
       </c>
       <c r="C67" s="71"/>
@@ -12949,7 +12980,7 @@
       <c r="J67" s="72"/>
     </row>
     <row r="68" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B68" s="79"/>
+      <c r="B68" s="82"/>
       <c r="C68" s="73"/>
       <c r="D68" s="35"/>
       <c r="E68" s="35"/>
@@ -12960,7 +12991,7 @@
       <c r="J68" s="35"/>
     </row>
     <row r="69" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B69" s="79"/>
+      <c r="B69" s="82"/>
       <c r="C69" s="73"/>
       <c r="D69" s="35"/>
       <c r="E69" s="35"/>
@@ -12971,7 +13002,7 @@
       <c r="J69" s="35"/>
     </row>
     <row r="70" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B70" s="79"/>
+      <c r="B70" s="82"/>
       <c r="C70" s="73"/>
       <c r="D70" s="35"/>
       <c r="E70" s="35"/>
@@ -12982,7 +13013,7 @@
       <c r="J70" s="35"/>
     </row>
     <row r="71" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B71" s="79"/>
+      <c r="B71" s="82"/>
       <c r="C71" s="73"/>
       <c r="D71" s="35"/>
       <c r="E71" s="35"/>
@@ -12993,7 +13024,7 @@
       <c r="J71" s="35"/>
     </row>
     <row r="72" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B72" s="79"/>
+      <c r="B72" s="82"/>
       <c r="C72" s="73"/>
       <c r="D72" s="35"/>
       <c r="E72" s="35"/>
@@ -13004,7 +13035,7 @@
       <c r="J72" s="35"/>
     </row>
     <row r="73" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B73" s="79"/>
+      <c r="B73" s="82"/>
       <c r="C73" s="73"/>
       <c r="D73" s="35"/>
       <c r="E73" s="35"/>
@@ -13015,7 +13046,7 @@
       <c r="J73" s="35"/>
     </row>
     <row r="74" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B74" s="80"/>
+      <c r="B74" s="83"/>
       <c r="C74" s="73"/>
       <c r="D74" s="35"/>
       <c r="E74" s="35"/>
